--- a/src/src/main/webapp/portal/wo/woExport/APM_WorkOrder_Template.xlsx
+++ b/src/src/main/webapp/portal/wo/woExport/APM_WorkOrder_Template.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
   <si>
     <t>报修单号</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -135,6 +135,10 @@
   </si>
   <si>
     <t>验收人</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>资产编号</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -483,32 +487,32 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:X2"/>
+  <dimension ref="A1:Y2"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="2" max="2" width="20.5" customWidth="1"/>
-    <col min="3" max="3" width="23.125" customWidth="1"/>
-    <col min="4" max="4" width="16.375" customWidth="1"/>
-    <col min="5" max="5" width="17.5" customWidth="1"/>
-    <col min="6" max="6" width="20.375" customWidth="1"/>
-    <col min="7" max="7" width="16.25" customWidth="1"/>
-    <col min="8" max="8" width="15.875" customWidth="1"/>
-    <col min="9" max="9" width="25.375" customWidth="1"/>
-    <col min="10" max="10" width="23" customWidth="1"/>
-    <col min="11" max="11" width="14.125" customWidth="1"/>
-    <col min="12" max="12" width="14.625" customWidth="1"/>
-    <col min="13" max="13" width="26.125" customWidth="1"/>
-    <col min="14" max="14" width="25" customWidth="1"/>
-    <col min="15" max="15" width="16.375" customWidth="1"/>
-    <col min="16" max="16" width="12.25" customWidth="1"/>
-    <col min="17" max="17" width="25" customWidth="1"/>
-    <col min="20" max="20" width="23.625" customWidth="1"/>
-    <col min="21" max="22" width="25.875" customWidth="1"/>
-    <col min="23" max="23" width="17" customWidth="1"/>
-    <col min="24" max="24" width="16.125" customWidth="1"/>
+    <col min="2" max="3" width="20.5" customWidth="1"/>
+    <col min="4" max="4" width="23.125" customWidth="1"/>
+    <col min="5" max="5" width="16.375" customWidth="1"/>
+    <col min="6" max="6" width="17.5" customWidth="1"/>
+    <col min="7" max="7" width="20.375" customWidth="1"/>
+    <col min="8" max="8" width="16.25" customWidth="1"/>
+    <col min="9" max="9" width="15.875" customWidth="1"/>
+    <col min="10" max="10" width="25.375" customWidth="1"/>
+    <col min="11" max="11" width="23" customWidth="1"/>
+    <col min="12" max="12" width="14.125" customWidth="1"/>
+    <col min="13" max="13" width="14.625" customWidth="1"/>
+    <col min="14" max="14" width="26.125" customWidth="1"/>
+    <col min="15" max="15" width="25" customWidth="1"/>
+    <col min="16" max="16" width="16.375" customWidth="1"/>
+    <col min="17" max="17" width="12.25" customWidth="1"/>
+    <col min="18" max="18" width="25" customWidth="1"/>
+    <col min="21" max="21" width="23.625" customWidth="1"/>
+    <col min="22" max="23" width="25.875" customWidth="1"/>
+    <col min="24" max="24" width="17" customWidth="1"/>
+    <col min="25" max="25" width="16.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" ht="16.5">
+    <row r="1" spans="1:25" ht="16.5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -516,74 +520,77 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="T1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="U1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="V1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="W1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="X1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="Y1" s="1" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:24">
-      <c r="Q2" s="2"/>
+    <row r="2" spans="1:25">
+      <c r="R2" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>

--- a/src/src/main/webapp/portal/wo/woExport/APM_WorkOrder_Template.xlsx
+++ b/src/src/main/webapp/portal/wo/woExport/APM_WorkOrder_Template.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
   <si>
     <t>报修单号</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -139,6 +139,10 @@
   </si>
   <si>
     <t>资产编号</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>工单状态</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -487,32 +491,32 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Y2"/>
+  <dimension ref="A1:Z2"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="2" max="3" width="20.5" customWidth="1"/>
-    <col min="4" max="4" width="23.125" customWidth="1"/>
-    <col min="5" max="5" width="16.375" customWidth="1"/>
-    <col min="6" max="6" width="17.5" customWidth="1"/>
-    <col min="7" max="7" width="20.375" customWidth="1"/>
-    <col min="8" max="8" width="16.25" customWidth="1"/>
-    <col min="9" max="9" width="15.875" customWidth="1"/>
-    <col min="10" max="10" width="25.375" customWidth="1"/>
-    <col min="11" max="11" width="23" customWidth="1"/>
-    <col min="12" max="12" width="14.125" customWidth="1"/>
-    <col min="13" max="13" width="14.625" customWidth="1"/>
-    <col min="14" max="14" width="26.125" customWidth="1"/>
-    <col min="15" max="15" width="25" customWidth="1"/>
-    <col min="16" max="16" width="16.375" customWidth="1"/>
-    <col min="17" max="17" width="12.25" customWidth="1"/>
-    <col min="18" max="18" width="25" customWidth="1"/>
-    <col min="21" max="21" width="23.625" customWidth="1"/>
-    <col min="22" max="23" width="25.875" customWidth="1"/>
-    <col min="24" max="24" width="17" customWidth="1"/>
-    <col min="25" max="25" width="16.125" customWidth="1"/>
+    <col min="4" max="5" width="23.125" customWidth="1"/>
+    <col min="6" max="6" width="16.375" customWidth="1"/>
+    <col min="7" max="7" width="17.5" customWidth="1"/>
+    <col min="8" max="8" width="20.375" customWidth="1"/>
+    <col min="9" max="9" width="16.25" customWidth="1"/>
+    <col min="10" max="10" width="15.875" customWidth="1"/>
+    <col min="11" max="11" width="25.375" customWidth="1"/>
+    <col min="12" max="12" width="23" customWidth="1"/>
+    <col min="13" max="13" width="14.125" customWidth="1"/>
+    <col min="14" max="14" width="14.625" customWidth="1"/>
+    <col min="15" max="15" width="26.125" customWidth="1"/>
+    <col min="16" max="16" width="25" customWidth="1"/>
+    <col min="17" max="17" width="16.375" customWidth="1"/>
+    <col min="18" max="18" width="12.25" customWidth="1"/>
+    <col min="19" max="19" width="25" customWidth="1"/>
+    <col min="22" max="22" width="23.625" customWidth="1"/>
+    <col min="23" max="24" width="25.875" customWidth="1"/>
+    <col min="25" max="25" width="17" customWidth="1"/>
+    <col min="26" max="26" width="16.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" ht="16.5">
+    <row r="1" spans="1:26" ht="16.5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -526,71 +530,74 @@
         <v>2</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="T1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="U1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="V1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="W1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="X1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="Y1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="Z1" s="1" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:25">
-      <c r="R2" s="2"/>
+    <row r="2" spans="1:26">
+      <c r="S2" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>

--- a/src/src/main/webapp/portal/wo/woExport/APM_WorkOrder_Template.xlsx
+++ b/src/src/main/webapp/portal/wo/woExport/APM_WorkOrder_Template.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
   <si>
     <t>报修单号</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -110,10 +110,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>价格</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>验收时间</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -143,6 +139,42 @@
   </si>
   <si>
     <t>工单状态</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>当前责任人</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>备注</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>当前步骤</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>解决方案</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>测试方法</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>问题描述</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>维修总费用</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>备件总费用</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>其他费用</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -491,32 +523,35 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Z2"/>
+  <dimension ref="A1:AH2"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="2" max="3" width="20.5" customWidth="1"/>
     <col min="4" max="5" width="23.125" customWidth="1"/>
     <col min="6" max="6" width="16.375" customWidth="1"/>
-    <col min="7" max="7" width="17.5" customWidth="1"/>
-    <col min="8" max="8" width="20.375" customWidth="1"/>
-    <col min="9" max="9" width="16.25" customWidth="1"/>
-    <col min="10" max="10" width="15.875" customWidth="1"/>
-    <col min="11" max="11" width="25.375" customWidth="1"/>
-    <col min="12" max="12" width="23" customWidth="1"/>
-    <col min="13" max="13" width="14.125" customWidth="1"/>
-    <col min="14" max="14" width="14.625" customWidth="1"/>
-    <col min="15" max="15" width="26.125" customWidth="1"/>
-    <col min="16" max="16" width="25" customWidth="1"/>
-    <col min="17" max="17" width="16.375" customWidth="1"/>
-    <col min="18" max="18" width="12.25" customWidth="1"/>
-    <col min="19" max="19" width="25" customWidth="1"/>
-    <col min="22" max="22" width="23.625" customWidth="1"/>
-    <col min="23" max="24" width="25.875" customWidth="1"/>
-    <col min="25" max="25" width="17" customWidth="1"/>
-    <col min="26" max="26" width="16.125" customWidth="1"/>
+    <col min="7" max="9" width="17.5" customWidth="1"/>
+    <col min="10" max="10" width="20.375" customWidth="1"/>
+    <col min="11" max="11" width="16.25" customWidth="1"/>
+    <col min="12" max="12" width="15.875" customWidth="1"/>
+    <col min="13" max="13" width="25.375" customWidth="1"/>
+    <col min="14" max="14" width="23" customWidth="1"/>
+    <col min="15" max="15" width="14.125" customWidth="1"/>
+    <col min="16" max="16" width="14.625" customWidth="1"/>
+    <col min="17" max="17" width="26.125" customWidth="1"/>
+    <col min="18" max="18" width="25" customWidth="1"/>
+    <col min="19" max="19" width="16.375" customWidth="1"/>
+    <col min="20" max="20" width="12.25" customWidth="1"/>
+    <col min="21" max="21" width="25" customWidth="1"/>
+    <col min="22" max="22" width="12.5" customWidth="1"/>
+    <col min="23" max="23" width="10.625" customWidth="1"/>
+    <col min="24" max="24" width="12.125" customWidth="1"/>
+    <col min="26" max="26" width="23.625" customWidth="1"/>
+    <col min="27" max="28" width="25.875" customWidth="1"/>
+    <col min="29" max="29" width="17" customWidth="1"/>
+    <col min="30" max="31" width="16.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" ht="16.5">
+    <row r="1" spans="1:34" ht="16.5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -524,13 +559,13 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>3</v>
@@ -539,65 +574,91 @@
         <v>4</v>
       </c>
       <c r="H1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="T1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="U1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="V1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="Z1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="U1" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="V1" s="1" t="s">
+      <c r="AA1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="AB1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="AC1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="AD1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="Z1" s="1" t="s">
-        <v>22</v>
+      <c r="AE1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="AF1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="AG1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AH1" s="1" t="s">
+        <v>26</v>
       </c>
     </row>
-    <row r="2" spans="1:26">
-      <c r="S2" s="2"/>
+    <row r="2" spans="1:34">
+      <c r="U2" s="2"/>
+      <c r="V2" s="2"/>
+      <c r="W2" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>

--- a/src/src/main/webapp/portal/wo/woExport/APM_WorkOrder_Template.xlsx
+++ b/src/src/main/webapp/portal/wo/woExport/APM_WorkOrder_Template.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="17726"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="18201"/>
   <workbookPr filterPrivacy="1"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7530"/>
@@ -9,7 +9,7 @@
   <sheets>
     <sheet name="WorkOrder List" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="171027"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="35">
   <si>
     <t>报修单号</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -175,6 +175,10 @@
   </si>
   <si>
     <t>其他费用</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>外修费用</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -523,7 +527,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AH2"/>
+  <dimension ref="A1:AI2"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="2" max="3" width="20.5" customWidth="1"/>
@@ -543,15 +547,15 @@
     <col min="20" max="20" width="12.25" customWidth="1"/>
     <col min="21" max="21" width="25" customWidth="1"/>
     <col min="22" max="22" width="12.5" customWidth="1"/>
-    <col min="23" max="23" width="10.625" customWidth="1"/>
-    <col min="24" max="24" width="12.125" customWidth="1"/>
-    <col min="26" max="26" width="23.625" customWidth="1"/>
-    <col min="27" max="28" width="25.875" customWidth="1"/>
-    <col min="29" max="29" width="17" customWidth="1"/>
-    <col min="30" max="31" width="16.125" customWidth="1"/>
+    <col min="23" max="24" width="10.625" customWidth="1"/>
+    <col min="25" max="25" width="12.125" customWidth="1"/>
+    <col min="27" max="27" width="23.625" customWidth="1"/>
+    <col min="28" max="29" width="25.875" customWidth="1"/>
+    <col min="30" max="30" width="17" customWidth="1"/>
+    <col min="31" max="32" width="16.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:34" ht="16.5">
+    <row r="1" spans="1:35" ht="16.5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -622,43 +626,47 @@
         <v>33</v>
       </c>
       <c r="X1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="Y1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="Z1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="Z1" s="1" t="s">
+      <c r="AA1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="AA1" s="1" t="s">
+      <c r="AB1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="AB1" s="1" t="s">
+      <c r="AC1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="AC1" s="1" t="s">
+      <c r="AD1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="AD1" s="1" t="s">
+      <c r="AE1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="AE1" s="1" t="s">
+      <c r="AF1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="AF1" s="1" t="s">
+      <c r="AG1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="AG1" s="1" t="s">
+      <c r="AH1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="AH1" s="1" t="s">
+      <c r="AI1" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="2" spans="1:34">
+    <row r="2" spans="1:35">
       <c r="U2" s="2"/>
       <c r="V2" s="2"/>
       <c r="W2" s="2"/>
+      <c r="X2" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>

--- a/src/src/main/webapp/portal/wo/woExport/APM_WorkOrder_Template.xlsx
+++ b/src/src/main/webapp/portal/wo/woExport/APM_WorkOrder_Template.xlsx
@@ -158,14 +158,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>测试方法</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>问题描述</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>维修总费用</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -179,6 +171,14 @@
   </si>
   <si>
     <t>外修费用</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>原因描述</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>交付前检测</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -620,16 +620,16 @@
         <v>16</v>
       </c>
       <c r="V1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="X1" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="W1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="X1" s="1" t="s">
-        <v>34</v>
-      </c>
       <c r="Y1" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="Z1" s="1" t="s">
         <v>22</v>
@@ -650,13 +650,13 @@
         <v>21</v>
       </c>
       <c r="AF1" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="AG1" s="1" t="s">
         <v>28</v>
       </c>
       <c r="AH1" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="AI1" s="1" t="s">
         <v>26</v>

--- a/src/src/main/webapp/portal/wo/woExport/APM_WorkOrder_Template.xlsx
+++ b/src/src/main/webapp/portal/wo/woExport/APM_WorkOrder_Template.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="37">
   <si>
     <t>报修单号</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -179,6 +179,14 @@
   </si>
   <si>
     <t>交付前检测</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>协助者</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>协助者工时</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -527,7 +535,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AI2"/>
+  <dimension ref="A1:AK2"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="2" max="3" width="20.5" customWidth="1"/>
@@ -550,12 +558,12 @@
     <col min="23" max="24" width="10.625" customWidth="1"/>
     <col min="25" max="25" width="12.125" customWidth="1"/>
     <col min="27" max="27" width="23.625" customWidth="1"/>
-    <col min="28" max="29" width="25.875" customWidth="1"/>
-    <col min="30" max="30" width="17" customWidth="1"/>
-    <col min="31" max="32" width="16.125" customWidth="1"/>
+    <col min="28" max="31" width="25.875" customWidth="1"/>
+    <col min="32" max="32" width="17" customWidth="1"/>
+    <col min="33" max="34" width="16.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35" ht="16.5">
+    <row r="1" spans="1:37" ht="16.5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -644,25 +652,31 @@
         <v>19</v>
       </c>
       <c r="AD1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="AE1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AF1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="AE1" s="1" t="s">
+      <c r="AG1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="AF1" s="1" t="s">
+      <c r="AH1" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="AG1" s="1" t="s">
+      <c r="AI1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="AH1" s="1" t="s">
+      <c r="AJ1" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="AI1" s="1" t="s">
+      <c r="AK1" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="2" spans="1:35">
+    <row r="2" spans="1:37">
       <c r="U2" s="2"/>
       <c r="V2" s="2"/>
       <c r="W2" s="2"/>

--- a/src/src/main/webapp/portal/wo/woExport/APM_WorkOrder_Template.xlsx
+++ b/src/src/main/webapp/portal/wo/woExport/APM_WorkOrder_Template.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="39">
   <si>
     <t>报修单号</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -187,6 +187,14 @@
   </si>
   <si>
     <t>协助者工时</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>品牌</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>制造商</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -535,35 +543,35 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AK2"/>
+  <dimension ref="A1:AM2"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="2" max="3" width="20.5" customWidth="1"/>
     <col min="4" max="5" width="23.125" customWidth="1"/>
     <col min="6" max="6" width="16.375" customWidth="1"/>
-    <col min="7" max="9" width="17.5" customWidth="1"/>
-    <col min="10" max="10" width="20.375" customWidth="1"/>
-    <col min="11" max="11" width="16.25" customWidth="1"/>
-    <col min="12" max="12" width="15.875" customWidth="1"/>
-    <col min="13" max="13" width="25.375" customWidth="1"/>
-    <col min="14" max="14" width="23" customWidth="1"/>
-    <col min="15" max="15" width="14.125" customWidth="1"/>
-    <col min="16" max="16" width="14.625" customWidth="1"/>
-    <col min="17" max="17" width="26.125" customWidth="1"/>
-    <col min="18" max="18" width="25" customWidth="1"/>
-    <col min="19" max="19" width="16.375" customWidth="1"/>
-    <col min="20" max="20" width="12.25" customWidth="1"/>
-    <col min="21" max="21" width="25" customWidth="1"/>
-    <col min="22" max="22" width="12.5" customWidth="1"/>
-    <col min="23" max="24" width="10.625" customWidth="1"/>
-    <col min="25" max="25" width="12.125" customWidth="1"/>
-    <col min="27" max="27" width="23.625" customWidth="1"/>
-    <col min="28" max="31" width="25.875" customWidth="1"/>
-    <col min="32" max="32" width="17" customWidth="1"/>
-    <col min="33" max="34" width="16.125" customWidth="1"/>
+    <col min="7" max="11" width="17.5" customWidth="1"/>
+    <col min="12" max="12" width="20.375" customWidth="1"/>
+    <col min="13" max="13" width="16.25" customWidth="1"/>
+    <col min="14" max="14" width="15.875" customWidth="1"/>
+    <col min="15" max="15" width="25.375" customWidth="1"/>
+    <col min="16" max="16" width="23" customWidth="1"/>
+    <col min="17" max="17" width="14.125" customWidth="1"/>
+    <col min="18" max="18" width="14.625" customWidth="1"/>
+    <col min="19" max="19" width="26.125" customWidth="1"/>
+    <col min="20" max="20" width="25" customWidth="1"/>
+    <col min="21" max="21" width="16.375" customWidth="1"/>
+    <col min="22" max="22" width="12.25" customWidth="1"/>
+    <col min="23" max="23" width="25" customWidth="1"/>
+    <col min="24" max="24" width="12.5" customWidth="1"/>
+    <col min="25" max="26" width="10.625" customWidth="1"/>
+    <col min="27" max="27" width="12.125" customWidth="1"/>
+    <col min="29" max="29" width="23.625" customWidth="1"/>
+    <col min="30" max="33" width="25.875" customWidth="1"/>
+    <col min="34" max="34" width="17" customWidth="1"/>
+    <col min="35" max="36" width="16.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:37" ht="16.5">
+    <row r="1" spans="1:39" ht="16.5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -586,101 +594,107 @@
         <v>4</v>
       </c>
       <c r="H1" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="J1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="T1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="U1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="V1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="W1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="X1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="Y1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="Z1" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="AA1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="Z1" s="1" t="s">
+      <c r="AB1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="AA1" s="1" t="s">
+      <c r="AC1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="AB1" s="1" t="s">
+      <c r="AD1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="AC1" s="1" t="s">
+      <c r="AE1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="AD1" s="1" t="s">
+      <c r="AF1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="AE1" s="1" t="s">
+      <c r="AG1" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AF1" s="1" t="s">
+      <c r="AH1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="AG1" s="1" t="s">
+      <c r="AI1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="AH1" s="1" t="s">
+      <c r="AJ1" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="AI1" s="1" t="s">
+      <c r="AK1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="AJ1" s="1" t="s">
+      <c r="AL1" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="AK1" s="1" t="s">
+      <c r="AM1" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="2" spans="1:37">
-      <c r="U2" s="2"/>
-      <c r="V2" s="2"/>
+    <row r="2" spans="1:39">
       <c r="W2" s="2"/>
       <c r="X2" s="2"/>
+      <c r="Y2" s="2"/>
+      <c r="Z2" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>

--- a/src/src/main/webapp/portal/wo/woExport/APM_WorkOrder_Template.xlsx
+++ b/src/src/main/webapp/portal/wo/woExport/APM_WorkOrder_Template.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="41">
   <si>
     <t>报修单号</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -195,6 +195,14 @@
   </si>
   <si>
     <t>制造商</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>设备序列号</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>维修完成时间</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -543,35 +551,35 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AM2"/>
+  <dimension ref="A1:AO2"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="2" max="3" width="20.5" customWidth="1"/>
-    <col min="4" max="5" width="23.125" customWidth="1"/>
-    <col min="6" max="6" width="16.375" customWidth="1"/>
-    <col min="7" max="11" width="17.5" customWidth="1"/>
-    <col min="12" max="12" width="20.375" customWidth="1"/>
-    <col min="13" max="13" width="16.25" customWidth="1"/>
-    <col min="14" max="14" width="15.875" customWidth="1"/>
-    <col min="15" max="15" width="25.375" customWidth="1"/>
-    <col min="16" max="16" width="23" customWidth="1"/>
-    <col min="17" max="17" width="14.125" customWidth="1"/>
-    <col min="18" max="18" width="14.625" customWidth="1"/>
-    <col min="19" max="19" width="26.125" customWidth="1"/>
-    <col min="20" max="20" width="25" customWidth="1"/>
-    <col min="21" max="21" width="16.375" customWidth="1"/>
-    <col min="22" max="22" width="12.25" customWidth="1"/>
-    <col min="23" max="23" width="25" customWidth="1"/>
-    <col min="24" max="24" width="12.5" customWidth="1"/>
-    <col min="25" max="26" width="10.625" customWidth="1"/>
-    <col min="27" max="27" width="12.125" customWidth="1"/>
-    <col min="29" max="29" width="23.625" customWidth="1"/>
-    <col min="30" max="33" width="25.875" customWidth="1"/>
-    <col min="34" max="34" width="17" customWidth="1"/>
-    <col min="35" max="36" width="16.125" customWidth="1"/>
+    <col min="2" max="4" width="20.5" customWidth="1"/>
+    <col min="5" max="6" width="23.125" customWidth="1"/>
+    <col min="7" max="7" width="16.375" customWidth="1"/>
+    <col min="8" max="12" width="17.5" customWidth="1"/>
+    <col min="13" max="13" width="20.375" customWidth="1"/>
+    <col min="14" max="14" width="16.25" customWidth="1"/>
+    <col min="15" max="15" width="15.875" customWidth="1"/>
+    <col min="16" max="16" width="25.375" customWidth="1"/>
+    <col min="17" max="17" width="23" customWidth="1"/>
+    <col min="18" max="18" width="14.125" customWidth="1"/>
+    <col min="19" max="19" width="14.625" customWidth="1"/>
+    <col min="20" max="20" width="26.125" customWidth="1"/>
+    <col min="21" max="21" width="25" customWidth="1"/>
+    <col min="22" max="23" width="16.375" customWidth="1"/>
+    <col min="24" max="24" width="12.25" customWidth="1"/>
+    <col min="25" max="25" width="25" customWidth="1"/>
+    <col min="26" max="26" width="12.5" customWidth="1"/>
+    <col min="27" max="28" width="10.625" customWidth="1"/>
+    <col min="29" max="29" width="12.125" customWidth="1"/>
+    <col min="31" max="31" width="23.625" customWidth="1"/>
+    <col min="32" max="35" width="25.875" customWidth="1"/>
+    <col min="36" max="36" width="17" customWidth="1"/>
+    <col min="37" max="38" width="16.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:39" ht="16.5">
+    <row r="1" spans="1:41" ht="16.5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -582,119 +590,125 @@
         <v>23</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="T1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="U1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="V1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="W1" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="X1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="Y1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="Z1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="AA1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="Z1" s="1" t="s">
+      <c r="AB1" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="AA1" s="1" t="s">
+      <c r="AC1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="AB1" s="1" t="s">
+      <c r="AD1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="AC1" s="1" t="s">
+      <c r="AE1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="AD1" s="1" t="s">
+      <c r="AF1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="AE1" s="1" t="s">
+      <c r="AG1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="AF1" s="1" t="s">
+      <c r="AH1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="AG1" s="1" t="s">
+      <c r="AI1" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AH1" s="1" t="s">
+      <c r="AJ1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="AI1" s="1" t="s">
+      <c r="AK1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="AJ1" s="1" t="s">
+      <c r="AL1" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="AK1" s="1" t="s">
+      <c r="AM1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="AL1" s="1" t="s">
+      <c r="AN1" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="AM1" s="1" t="s">
+      <c r="AO1" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="2" spans="1:39">
-      <c r="W2" s="2"/>
-      <c r="X2" s="2"/>
+    <row r="2" spans="1:41">
       <c r="Y2" s="2"/>
       <c r="Z2" s="2"/>
+      <c r="AA2" s="2"/>
+      <c r="AB2" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>

--- a/src/src/main/webapp/portal/wo/woExport/APM_WorkOrder_Template.xlsx
+++ b/src/src/main/webapp/portal/wo/woExport/APM_WorkOrder_Template.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="18201"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="18431"/>
   <workbookPr filterPrivacy="1"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7530"/>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="46">
   <si>
     <t>报修单号</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -205,12 +205,32 @@
     <t>维修完成时间</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
+  <si>
+    <t>二维码</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>设备分类</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>医疗器械分类</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>医疗器械子分类</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>设备型号</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="5">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -551,35 +571,35 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AO2"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <dimension ref="A1:AT2"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="4" width="20.5" customWidth="1"/>
     <col min="5" max="6" width="23.125" customWidth="1"/>
     <col min="7" max="7" width="16.375" customWidth="1"/>
-    <col min="8" max="12" width="17.5" customWidth="1"/>
-    <col min="13" max="13" width="20.375" customWidth="1"/>
-    <col min="14" max="14" width="16.25" customWidth="1"/>
-    <col min="15" max="15" width="15.875" customWidth="1"/>
-    <col min="16" max="16" width="25.375" customWidth="1"/>
-    <col min="17" max="17" width="23" customWidth="1"/>
-    <col min="18" max="18" width="14.125" customWidth="1"/>
-    <col min="19" max="19" width="14.625" customWidth="1"/>
-    <col min="20" max="20" width="26.125" customWidth="1"/>
-    <col min="21" max="21" width="25" customWidth="1"/>
-    <col min="22" max="23" width="16.375" customWidth="1"/>
-    <col min="24" max="24" width="12.25" customWidth="1"/>
-    <col min="25" max="25" width="25" customWidth="1"/>
-    <col min="26" max="26" width="12.5" customWidth="1"/>
-    <col min="27" max="28" width="10.625" customWidth="1"/>
-    <col min="29" max="29" width="12.125" customWidth="1"/>
-    <col min="31" max="31" width="23.625" customWidth="1"/>
-    <col min="32" max="35" width="25.875" customWidth="1"/>
-    <col min="36" max="36" width="17" customWidth="1"/>
-    <col min="37" max="38" width="16.125" customWidth="1"/>
+    <col min="8" max="17" width="17.5" customWidth="1"/>
+    <col min="18" max="18" width="20.375" customWidth="1"/>
+    <col min="19" max="19" width="16.25" customWidth="1"/>
+    <col min="20" max="20" width="15.875" customWidth="1"/>
+    <col min="21" max="21" width="25.375" customWidth="1"/>
+    <col min="22" max="22" width="23" customWidth="1"/>
+    <col min="23" max="23" width="14.125" customWidth="1"/>
+    <col min="24" max="24" width="14.625" customWidth="1"/>
+    <col min="25" max="25" width="26.125" customWidth="1"/>
+    <col min="26" max="26" width="25" customWidth="1"/>
+    <col min="27" max="28" width="16.375" customWidth="1"/>
+    <col min="29" max="29" width="12.25" customWidth="1"/>
+    <col min="30" max="30" width="25" customWidth="1"/>
+    <col min="31" max="31" width="12.5" customWidth="1"/>
+    <col min="32" max="33" width="10.625" customWidth="1"/>
+    <col min="34" max="34" width="12.125" customWidth="1"/>
+    <col min="36" max="36" width="23.625" customWidth="1"/>
+    <col min="37" max="40" width="25.875" customWidth="1"/>
+    <col min="41" max="41" width="17" customWidth="1"/>
+    <col min="42" max="43" width="16.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:41" ht="16.5">
+    <row r="1" spans="1:46" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -611,104 +631,119 @@
         <v>37</v>
       </c>
       <c r="K1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="P1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="T1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="U1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="V1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="W1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="X1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="Y1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="Z1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="AA1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="AB1" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="AC1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="AD1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="Z1" s="1" t="s">
+      <c r="AE1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="AA1" s="1" t="s">
+      <c r="AF1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="AB1" s="1" t="s">
+      <c r="AG1" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="AC1" s="1" t="s">
+      <c r="AH1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="AD1" s="1" t="s">
+      <c r="AI1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="AE1" s="1" t="s">
+      <c r="AJ1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="AF1" s="1" t="s">
+      <c r="AK1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="AG1" s="1" t="s">
+      <c r="AL1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="AH1" s="1" t="s">
+      <c r="AM1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="AI1" s="1" t="s">
+      <c r="AN1" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AJ1" s="1" t="s">
+      <c r="AO1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="AK1" s="1" t="s">
+      <c r="AP1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="AL1" s="1" t="s">
+      <c r="AQ1" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="AM1" s="1" t="s">
+      <c r="AR1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="AN1" s="1" t="s">
+      <c r="AS1" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="AO1" s="1" t="s">
+      <c r="AT1" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="2" spans="1:41">
-      <c r="Y2" s="2"/>
-      <c r="Z2" s="2"/>
-      <c r="AA2" s="2"/>
-      <c r="AB2" s="2"/>
+    <row r="2" spans="1:46" x14ac:dyDescent="0.2">
+      <c r="AD2" s="2"/>
+      <c r="AE2" s="2"/>
+      <c r="AF2" s="2"/>
+      <c r="AG2" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>

--- a/src/src/main/webapp/portal/wo/woExport/APM_WorkOrder_Template.xlsx
+++ b/src/src/main/webapp/portal/wo/woExport/APM_WorkOrder_Template.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="47">
   <si>
     <t>报修单号</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -223,6 +223,10 @@
   </si>
   <si>
     <t>设备型号</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>距上次报修天数</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -571,7 +575,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AT2"/>
+  <dimension ref="A1:AU2"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="4" width="20.5" customWidth="1"/>
@@ -594,12 +598,15 @@
     <col min="32" max="33" width="10.625" customWidth="1"/>
     <col min="34" max="34" width="12.125" customWidth="1"/>
     <col min="36" max="36" width="23.625" customWidth="1"/>
-    <col min="37" max="40" width="25.875" customWidth="1"/>
-    <col min="41" max="41" width="17" customWidth="1"/>
-    <col min="42" max="43" width="16.125" customWidth="1"/>
+    <col min="37" max="38" width="25.875" customWidth="1"/>
+    <col min="39" max="39" width="21" customWidth="1"/>
+    <col min="40" max="40" width="25.875" customWidth="1"/>
+    <col min="41" max="41" width="16.25" customWidth="1"/>
+    <col min="42" max="42" width="17" customWidth="1"/>
+    <col min="43" max="44" width="16.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:46" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:47" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -721,25 +728,28 @@
         <v>36</v>
       </c>
       <c r="AO1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="AP1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="AP1" s="1" t="s">
+      <c r="AQ1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="AQ1" s="1" t="s">
+      <c r="AR1" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="AR1" s="1" t="s">
+      <c r="AS1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="AS1" s="1" t="s">
+      <c r="AT1" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="AT1" s="1" t="s">
+      <c r="AU1" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="2" spans="1:46" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:47" x14ac:dyDescent="0.2">
       <c r="AD2" s="2"/>
       <c r="AE2" s="2"/>
       <c r="AF2" s="2"/>

--- a/src/src/main/webapp/portal/wo/woExport/APM_WorkOrder_Template.xlsx
+++ b/src/src/main/webapp/portal/wo/woExport/APM_WorkOrder_Template.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="49">
   <si>
     <t>报修单号</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -227,6 +227,14 @@
   </si>
   <si>
     <t>距上次报修天数</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>停机时间</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>恢复时间</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -575,7 +583,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AU2"/>
+  <dimension ref="A1:AW2"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="4" width="20.5" customWidth="1"/>
@@ -600,13 +608,13 @@
     <col min="36" max="36" width="23.625" customWidth="1"/>
     <col min="37" max="38" width="25.875" customWidth="1"/>
     <col min="39" max="39" width="21" customWidth="1"/>
-    <col min="40" max="40" width="25.875" customWidth="1"/>
-    <col min="41" max="41" width="16.25" customWidth="1"/>
-    <col min="42" max="42" width="17" customWidth="1"/>
-    <col min="43" max="44" width="16.125" customWidth="1"/>
+    <col min="40" max="42" width="25.875" customWidth="1"/>
+    <col min="43" max="43" width="16.25" customWidth="1"/>
+    <col min="44" max="44" width="17" customWidth="1"/>
+    <col min="45" max="46" width="16.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:47" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:49" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -728,28 +736,34 @@
         <v>36</v>
       </c>
       <c r="AO1" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="AP1" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="AQ1" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="AP1" s="1" t="s">
+      <c r="AR1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="AQ1" s="1" t="s">
+      <c r="AS1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="AR1" s="1" t="s">
+      <c r="AT1" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="AS1" s="1" t="s">
+      <c r="AU1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="AT1" s="1" t="s">
+      <c r="AV1" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="AU1" s="1" t="s">
+      <c r="AW1" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="2" spans="1:47" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:49" x14ac:dyDescent="0.2">
       <c r="AD2" s="2"/>
       <c r="AE2" s="2"/>
       <c r="AF2" s="2"/>

--- a/src/src/main/webapp/portal/wo/woExport/APM_WorkOrder_Template.xlsx
+++ b/src/src/main/webapp/portal/wo/woExport/APM_WorkOrder_Template.xlsx
@@ -1,10 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="18431"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="19126"/>
   <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="10_ncr:100000_{D2ADD5DE-7B40-4553-9DBE-12984A11CDDE}" xr6:coauthVersionLast="31" xr6:coauthVersionMax="31" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7530"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7530" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="WorkOrder List" sheetId="1" r:id="rId1"/>
@@ -19,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="50">
   <si>
     <t>报修单号</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -102,10 +103,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>维修工时</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>维修备件</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -235,13 +232,21 @@
   </si>
   <si>
     <t>恢复时间</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>维修总工时</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>维修工程师工时</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -582,8 +587,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AW2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:AX2"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="4" width="20.5" customWidth="1"/>
@@ -599,22 +604,22 @@
     <col min="24" max="24" width="14.625" customWidth="1"/>
     <col min="25" max="25" width="26.125" customWidth="1"/>
     <col min="26" max="26" width="25" customWidth="1"/>
-    <col min="27" max="28" width="16.375" customWidth="1"/>
-    <col min="29" max="29" width="12.25" customWidth="1"/>
-    <col min="30" max="30" width="25" customWidth="1"/>
-    <col min="31" max="31" width="12.5" customWidth="1"/>
-    <col min="32" max="33" width="10.625" customWidth="1"/>
-    <col min="34" max="34" width="12.125" customWidth="1"/>
-    <col min="36" max="36" width="23.625" customWidth="1"/>
-    <col min="37" max="38" width="25.875" customWidth="1"/>
-    <col min="39" max="39" width="21" customWidth="1"/>
-    <col min="40" max="42" width="25.875" customWidth="1"/>
-    <col min="43" max="43" width="16.25" customWidth="1"/>
-    <col min="44" max="44" width="17" customWidth="1"/>
-    <col min="45" max="46" width="16.125" customWidth="1"/>
+    <col min="27" max="29" width="16.375" customWidth="1"/>
+    <col min="30" max="30" width="12.25" customWidth="1"/>
+    <col min="31" max="31" width="25" customWidth="1"/>
+    <col min="32" max="32" width="12.5" customWidth="1"/>
+    <col min="33" max="34" width="10.625" customWidth="1"/>
+    <col min="35" max="35" width="12.125" customWidth="1"/>
+    <col min="37" max="37" width="23.625" customWidth="1"/>
+    <col min="38" max="39" width="25.875" customWidth="1"/>
+    <col min="40" max="40" width="21" customWidth="1"/>
+    <col min="41" max="43" width="25.875" customWidth="1"/>
+    <col min="44" max="44" width="16.25" customWidth="1"/>
+    <col min="45" max="45" width="17" customWidth="1"/>
+    <col min="46" max="47" width="16.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:49" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:50" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -622,16 +627,16 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>3</v>
@@ -640,31 +645,31 @@
         <v>4</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="K1" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="L1" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="O1" s="1" t="s">
-        <v>45</v>
-      </c>
       <c r="P1" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="R1" s="1" t="s">
         <v>5</v>
@@ -697,77 +702,80 @@
         <v>14</v>
       </c>
       <c r="AB1" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="AC1" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="AD1" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="AE1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="AD1" s="1" t="s">
+      <c r="AF1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AG1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="AH1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="AI1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="AJ1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="AK1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="AE1" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="AF1" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="AG1" s="1" t="s">
+      <c r="AL1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="AM1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="AN1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="AO1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="AP1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="AQ1" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="AR1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="AS1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="AT1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="AU1" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="AH1" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="AI1" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="AJ1" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="AK1" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="AL1" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="AM1" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="AN1" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="AO1" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="AP1" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="AQ1" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="AR1" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="AS1" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="AT1" s="1" t="s">
+      <c r="AV1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AW1" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="AU1" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="AV1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="AW1" s="1" t="s">
-        <v>26</v>
+      <c r="AX1" s="1" t="s">
+        <v>25</v>
       </c>
     </row>
-    <row r="2" spans="1:49" x14ac:dyDescent="0.2">
-      <c r="AD2" s="2"/>
+    <row r="2" spans="1:50" x14ac:dyDescent="0.2">
       <c r="AE2" s="2"/>
       <c r="AF2" s="2"/>
       <c r="AG2" s="2"/>
+      <c r="AH2" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>

--- a/src/src/main/webapp/portal/wo/woExport/APM_WorkOrder_Template.xlsx
+++ b/src/src/main/webapp/portal/wo/woExport/APM_WorkOrder_Template.xlsx
@@ -3,12 +3,13 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="19126"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="10_ncr:100000_{D2ADD5DE-7B40-4553-9DBE-12984A11CDDE}" xr6:coauthVersionLast="31" xr6:coauthVersionMax="31" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="10_ncr:100000_{4782866D-EA91-4AF0-9401-A3C487F12D96}" xr6:coauthVersionLast="31" xr6:coauthVersionMax="31" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7530" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="WorkOrder List" sheetId="1" r:id="rId1"/>
+    <sheet name="Parts List" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="171027"/>
   <extLst>
@@ -20,234 +21,245 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="58">
   <si>
     <t>报修单号</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>设备编号</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>设备名称</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>院区</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>科室</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>报修人</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>报修时间</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>故障描述</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>派工人</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>派工时间</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>工单类型</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>上门维修</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>送修</t>
-    </r>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>接单人</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>接单时间</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>签到时间</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>维修备件</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>验收时间</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>关单人</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>关单时间</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>最终评价</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>故障类型</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>验收人</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>资产编号</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>工单状态</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>当前责任人</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>备注</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>当前步骤</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>解决方案</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>维修总费用</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>备件总费用</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>其他费用</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>外修费用</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>原因描述</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>交付前检测</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>协助者</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>协助者工时</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>品牌</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>制造商</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>设备序列号</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>维修完成时间</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>二维码</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>设备分类</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>医疗器械分类</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>医疗器械子分类</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>设备型号</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>距上次报修天数</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>停机时间</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>恢复时间</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>维修总工时</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>维修工程师工时</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>备件名</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>单价</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>数量</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>合同号</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>发票号</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>开票日期</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>预计价格</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>供应商</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>维修类型</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -261,12 +273,6 @@
       <name val="微软雅黑"/>
       <family val="2"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="9"/>
@@ -307,7 +313,7 @@
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -627,16 +633,16 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>3</v>
@@ -645,31 +651,31 @@
         <v>4</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="K1" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="L1" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="O1" s="1" t="s">
-        <v>44</v>
-      </c>
       <c r="P1" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="R1" s="1" t="s">
         <v>5</v>
@@ -690,85 +696,85 @@
         <v>10</v>
       </c>
       <c r="X1" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="Y1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="Z1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="Z1" s="1" t="s">
+      <c r="AA1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="AA1" s="1" t="s">
+      <c r="AB1" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="AC1" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="AD1" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="AE1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="AB1" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="AC1" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="AD1" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="AE1" s="1" t="s">
+      <c r="AF1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="AG1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AH1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="AI1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AJ1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="AK1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="AF1" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="AG1" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="AH1" s="1" t="s">
+      <c r="AL1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="AM1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="AN1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AO1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="AP1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="AQ1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="AR1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="AS1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="AT1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="AU1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="AI1" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="AJ1" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="AK1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="AL1" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="AM1" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="AN1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="AO1" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="AP1" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="AQ1" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="AR1" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="AS1" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="AT1" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="AU1" s="1" t="s">
+      <c r="AV1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AW1" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="AV1" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="AW1" s="1" t="s">
-        <v>33</v>
-      </c>
       <c r="AX1" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="2" spans="1:50" x14ac:dyDescent="0.2">
@@ -778,7 +784,51 @@
       <c r="AH2" s="2"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{71B27B56-1823-4D07-9234-02F082420C5C}">
+  <dimension ref="A1:J1"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D1" t="s">
+        <v>51</v>
+      </c>
+      <c r="E1" t="s">
+        <v>52</v>
+      </c>
+      <c r="F1" t="s">
+        <v>53</v>
+      </c>
+      <c r="G1" t="s">
+        <v>54</v>
+      </c>
+      <c r="H1" t="s">
+        <v>55</v>
+      </c>
+      <c r="I1" t="s">
+        <v>56</v>
+      </c>
+      <c r="J1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/src/src/main/webapp/portal/wo/woExport/APM_WorkOrder_Template.xlsx
+++ b/src/src/main/webapp/portal/wo/woExport/APM_WorkOrder_Template.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="19126"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="10_ncr:100000_{4782866D-EA91-4AF0-9401-A3C487F12D96}" xr6:coauthVersionLast="31" xr6:coauthVersionMax="31" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="10_ncr:100000_{40688751-131E-4145-A310-472DD7C4A3E8}" xr6:coauthVersionLast="31" xr6:coauthVersionMax="31" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7530" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -199,10 +199,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>距上次报修天数</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>停机时间</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -252,6 +248,10 @@
   </si>
   <si>
     <t>维修类型</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>修复后无故障天数</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -696,7 +696,7 @@
         <v>10</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="Y1" s="1" t="s">
         <v>11</v>
@@ -711,10 +711,10 @@
         <v>38</v>
       </c>
       <c r="AC1" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="AD1" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="AE1" s="1" t="s">
         <v>14</v>
@@ -750,13 +750,13 @@
         <v>34</v>
       </c>
       <c r="AP1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="AQ1" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="AQ1" s="1" t="s">
-        <v>46</v>
-      </c>
       <c r="AR1" s="1" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="AS1" s="1" t="s">
         <v>18</v>
@@ -800,28 +800,28 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C1" t="s">
         <v>49</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>50</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>51</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>52</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>53</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>54</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>55</v>
-      </c>
-      <c r="I1" t="s">
-        <v>56</v>
       </c>
       <c r="J1" t="s">
         <v>24</v>

--- a/src/src/main/webapp/portal/wo/woExport/APM_WorkOrder_Template.xlsx
+++ b/src/src/main/webapp/portal/wo/woExport/APM_WorkOrder_Template.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="19126"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20730"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="10_ncr:100000_{40688751-131E-4145-A310-472DD7C4A3E8}" xr6:coauthVersionLast="31" xr6:coauthVersionMax="31" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42B2E8DA-027A-43A9-98F8-C9A7EAE70EB4}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7530" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7530" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="WorkOrder List" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="60">
   <si>
     <t>报修单号</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -219,10 +219,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>单价</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>数量</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -252,6 +248,18 @@
   </si>
   <si>
     <t>修复后无故障天数</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>合同价格</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>设备编号</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>资产名称</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -595,37 +603,37 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AX2"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="4" width="20.5" customWidth="1"/>
-    <col min="5" max="6" width="23.125" customWidth="1"/>
-    <col min="7" max="7" width="16.375" customWidth="1"/>
-    <col min="8" max="17" width="17.5" customWidth="1"/>
-    <col min="18" max="18" width="20.375" customWidth="1"/>
-    <col min="19" max="19" width="16.25" customWidth="1"/>
-    <col min="20" max="20" width="15.875" customWidth="1"/>
-    <col min="21" max="21" width="25.375" customWidth="1"/>
+    <col min="2" max="4" width="20.44140625" customWidth="1"/>
+    <col min="5" max="6" width="23.109375" customWidth="1"/>
+    <col min="7" max="7" width="16.33203125" customWidth="1"/>
+    <col min="8" max="17" width="17.44140625" customWidth="1"/>
+    <col min="18" max="18" width="20.33203125" customWidth="1"/>
+    <col min="19" max="19" width="16.21875" customWidth="1"/>
+    <col min="20" max="20" width="15.88671875" customWidth="1"/>
+    <col min="21" max="21" width="25.33203125" customWidth="1"/>
     <col min="22" max="22" width="23" customWidth="1"/>
-    <col min="23" max="23" width="14.125" customWidth="1"/>
-    <col min="24" max="24" width="14.625" customWidth="1"/>
-    <col min="25" max="25" width="26.125" customWidth="1"/>
+    <col min="23" max="23" width="14.109375" customWidth="1"/>
+    <col min="24" max="24" width="14.6640625" customWidth="1"/>
+    <col min="25" max="25" width="26.109375" customWidth="1"/>
     <col min="26" max="26" width="25" customWidth="1"/>
-    <col min="27" max="29" width="16.375" customWidth="1"/>
-    <col min="30" max="30" width="12.25" customWidth="1"/>
+    <col min="27" max="29" width="16.33203125" customWidth="1"/>
+    <col min="30" max="30" width="12.21875" customWidth="1"/>
     <col min="31" max="31" width="25" customWidth="1"/>
-    <col min="32" max="32" width="12.5" customWidth="1"/>
-    <col min="33" max="34" width="10.625" customWidth="1"/>
-    <col min="35" max="35" width="12.125" customWidth="1"/>
-    <col min="37" max="37" width="23.625" customWidth="1"/>
-    <col min="38" max="39" width="25.875" customWidth="1"/>
+    <col min="32" max="32" width="12.44140625" customWidth="1"/>
+    <col min="33" max="34" width="10.6640625" customWidth="1"/>
+    <col min="35" max="35" width="12.109375" customWidth="1"/>
+    <col min="37" max="37" width="23.6640625" customWidth="1"/>
+    <col min="38" max="39" width="25.88671875" customWidth="1"/>
     <col min="40" max="40" width="21" customWidth="1"/>
-    <col min="41" max="43" width="25.875" customWidth="1"/>
-    <col min="44" max="44" width="16.25" customWidth="1"/>
+    <col min="41" max="43" width="25.88671875" customWidth="1"/>
+    <col min="44" max="44" width="16.21875" customWidth="1"/>
     <col min="45" max="45" width="17" customWidth="1"/>
-    <col min="46" max="47" width="16.125" customWidth="1"/>
+    <col min="46" max="47" width="16.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:50" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -696,7 +704,7 @@
         <v>10</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="Y1" s="1" t="s">
         <v>11</v>
@@ -756,7 +764,7 @@
         <v>45</v>
       </c>
       <c r="AR1" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="AS1" s="1" t="s">
         <v>18</v>
@@ -777,7 +785,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:50" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:50" x14ac:dyDescent="0.3">
       <c r="AE2" s="2"/>
       <c r="AF2" s="2"/>
       <c r="AG2" s="2"/>
@@ -792,38 +800,47 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{71B27B56-1823-4D07-9234-02F082420C5C}">
-  <dimension ref="A1:J1"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:L1"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="3" max="3" width="10.88671875" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C1" t="s">
+        <v>58</v>
+      </c>
+      <c r="D1" t="s">
         <v>48</v>
       </c>
-      <c r="C1" t="s">
+      <c r="E1" t="s">
+        <v>57</v>
+      </c>
+      <c r="F1" t="s">
         <v>49</v>
       </c>
-      <c r="D1" t="s">
+      <c r="G1" t="s">
         <v>50</v>
       </c>
-      <c r="E1" t="s">
+      <c r="H1" t="s">
         <v>51</v>
       </c>
-      <c r="F1" t="s">
+      <c r="I1" t="s">
         <v>52</v>
       </c>
-      <c r="G1" t="s">
+      <c r="J1" t="s">
         <v>53</v>
       </c>
-      <c r="H1" t="s">
+      <c r="K1" t="s">
         <v>54</v>
       </c>
-      <c r="I1" t="s">
-        <v>55</v>
-      </c>
-      <c r="J1" t="s">
+      <c r="L1" t="s">
         <v>24</v>
       </c>
     </row>

--- a/src/src/main/webapp/portal/wo/woExport/APM_WorkOrder_Template.xlsx
+++ b/src/src/main/webapp/portal/wo/woExport/APM_WorkOrder_Template.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20730"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42B2E8DA-027A-43A9-98F8-C9A7EAE70EB4}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9598F08F-C156-4D5D-92D7-9DFA48DFF683}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7530" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7530" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="WorkOrder List" sheetId="1" r:id="rId1"/>
@@ -603,37 +603,37 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AX2"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="4" width="20.44140625" customWidth="1"/>
-    <col min="5" max="6" width="23.109375" customWidth="1"/>
-    <col min="7" max="7" width="16.33203125" customWidth="1"/>
-    <col min="8" max="17" width="17.44140625" customWidth="1"/>
-    <col min="18" max="18" width="20.33203125" customWidth="1"/>
-    <col min="19" max="19" width="16.21875" customWidth="1"/>
-    <col min="20" max="20" width="15.88671875" customWidth="1"/>
-    <col min="21" max="21" width="25.33203125" customWidth="1"/>
+    <col min="2" max="4" width="20.5" customWidth="1"/>
+    <col min="5" max="6" width="23.125" customWidth="1"/>
+    <col min="7" max="7" width="16.375" customWidth="1"/>
+    <col min="8" max="17" width="17.5" customWidth="1"/>
+    <col min="18" max="18" width="20.375" customWidth="1"/>
+    <col min="19" max="19" width="16.25" customWidth="1"/>
+    <col min="20" max="20" width="15.875" customWidth="1"/>
+    <col min="21" max="21" width="25.375" customWidth="1"/>
     <col min="22" max="22" width="23" customWidth="1"/>
-    <col min="23" max="23" width="14.109375" customWidth="1"/>
-    <col min="24" max="24" width="14.6640625" customWidth="1"/>
-    <col min="25" max="25" width="26.109375" customWidth="1"/>
+    <col min="23" max="23" width="14.125" customWidth="1"/>
+    <col min="24" max="24" width="14.625" customWidth="1"/>
+    <col min="25" max="25" width="26.125" customWidth="1"/>
     <col min="26" max="26" width="25" customWidth="1"/>
-    <col min="27" max="29" width="16.33203125" customWidth="1"/>
-    <col min="30" max="30" width="12.21875" customWidth="1"/>
+    <col min="27" max="29" width="16.375" customWidth="1"/>
+    <col min="30" max="30" width="12.25" customWidth="1"/>
     <col min="31" max="31" width="25" customWidth="1"/>
-    <col min="32" max="32" width="12.44140625" customWidth="1"/>
-    <col min="33" max="34" width="10.6640625" customWidth="1"/>
-    <col min="35" max="35" width="12.109375" customWidth="1"/>
-    <col min="37" max="37" width="23.6640625" customWidth="1"/>
-    <col min="38" max="39" width="25.88671875" customWidth="1"/>
+    <col min="32" max="32" width="12.5" customWidth="1"/>
+    <col min="33" max="34" width="10.625" customWidth="1"/>
+    <col min="35" max="35" width="12.125" customWidth="1"/>
+    <col min="37" max="37" width="23.625" customWidth="1"/>
+    <col min="38" max="39" width="25.875" customWidth="1"/>
     <col min="40" max="40" width="21" customWidth="1"/>
-    <col min="41" max="43" width="25.88671875" customWidth="1"/>
-    <col min="44" max="44" width="16.21875" customWidth="1"/>
+    <col min="41" max="43" width="25.875" customWidth="1"/>
+    <col min="44" max="44" width="16.25" customWidth="1"/>
     <col min="45" max="45" width="17" customWidth="1"/>
-    <col min="46" max="47" width="16.109375" customWidth="1"/>
+    <col min="46" max="47" width="16.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:50" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:50" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -785,7 +785,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:50" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:50" x14ac:dyDescent="0.2">
       <c r="AE2" s="2"/>
       <c r="AF2" s="2"/>
       <c r="AG2" s="2"/>
@@ -801,12 +801,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{71B27B56-1823-4D07-9234-02F082420C5C}">
   <dimension ref="A1:L1"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="3" max="3" width="10.88671875" customWidth="1"/>
+    <col min="3" max="3" width="10.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>

--- a/src/src/main/webapp/portal/wo/woExport/APM_WorkOrder_Template.xlsx
+++ b/src/src/main/webapp/portal/wo/woExport/APM_WorkOrder_Template.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20730"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9598F08F-C156-4D5D-92D7-9DFA48DFF683}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F01B7AA2-8947-4A72-A424-B2216EE1FFF8}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7530" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="61">
   <si>
     <t>报修单号</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -260,6 +260,10 @@
   </si>
   <si>
     <t>资产名称</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>报修人电话</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -602,7 +606,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AX2"/>
+  <dimension ref="A1:AY2"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="4" width="20.5" customWidth="1"/>
@@ -610,30 +614,32 @@
     <col min="7" max="7" width="16.375" customWidth="1"/>
     <col min="8" max="17" width="17.5" customWidth="1"/>
     <col min="18" max="18" width="20.375" customWidth="1"/>
-    <col min="19" max="19" width="16.25" customWidth="1"/>
-    <col min="20" max="20" width="15.875" customWidth="1"/>
-    <col min="21" max="21" width="25.375" customWidth="1"/>
-    <col min="22" max="22" width="23" customWidth="1"/>
-    <col min="23" max="23" width="14.125" customWidth="1"/>
-    <col min="24" max="24" width="14.625" customWidth="1"/>
-    <col min="25" max="25" width="26.125" customWidth="1"/>
-    <col min="26" max="26" width="25" customWidth="1"/>
-    <col min="27" max="29" width="16.375" customWidth="1"/>
-    <col min="30" max="30" width="12.25" customWidth="1"/>
-    <col min="31" max="31" width="25" customWidth="1"/>
-    <col min="32" max="32" width="12.5" customWidth="1"/>
-    <col min="33" max="34" width="10.625" customWidth="1"/>
-    <col min="35" max="35" width="12.125" customWidth="1"/>
-    <col min="37" max="37" width="23.625" customWidth="1"/>
-    <col min="38" max="39" width="25.875" customWidth="1"/>
-    <col min="40" max="40" width="21" customWidth="1"/>
-    <col min="41" max="43" width="25.875" customWidth="1"/>
-    <col min="44" max="44" width="16.25" customWidth="1"/>
-    <col min="45" max="45" width="17" customWidth="1"/>
-    <col min="46" max="47" width="16.125" customWidth="1"/>
+    <col min="19" max="20" width="16.25" customWidth="1"/>
+    <col min="21" max="21" width="15.875" customWidth="1"/>
+    <col min="22" max="22" width="25.375" customWidth="1"/>
+    <col min="23" max="23" width="23" customWidth="1"/>
+    <col min="24" max="24" width="14.125" customWidth="1"/>
+    <col min="25" max="25" width="14.625" customWidth="1"/>
+    <col min="26" max="26" width="26.125" customWidth="1"/>
+    <col min="27" max="27" width="25" customWidth="1"/>
+    <col min="28" max="30" width="16.375" customWidth="1"/>
+    <col min="31" max="31" width="12.25" customWidth="1"/>
+    <col min="32" max="32" width="25" customWidth="1"/>
+    <col min="33" max="33" width="12.5" customWidth="1"/>
+    <col min="34" max="35" width="10.625" customWidth="1"/>
+    <col min="36" max="36" width="12.125" customWidth="1"/>
+    <col min="38" max="38" width="23.625" customWidth="1"/>
+    <col min="39" max="40" width="25.875" customWidth="1"/>
+    <col min="41" max="41" width="21" customWidth="1"/>
+    <col min="42" max="44" width="25.875" customWidth="1"/>
+    <col min="45" max="45" width="16.25" customWidth="1"/>
+    <col min="46" max="46" width="17" customWidth="1"/>
+    <col min="47" max="48" width="16.125" customWidth="1"/>
+    <col min="49" max="49" width="9.375" customWidth="1"/>
+    <col min="50" max="50" width="12.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:50" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:51" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -692,104 +698,107 @@
         <v>6</v>
       </c>
       <c r="T1" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="U1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="V1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="W1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="X1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="Y1" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="Z1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="Z1" s="1" t="s">
+      <c r="AA1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="AA1" s="1" t="s">
+      <c r="AB1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="AB1" s="1" t="s">
+      <c r="AC1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="AC1" s="1" t="s">
+      <c r="AD1" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="AD1" s="1" t="s">
+      <c r="AE1" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="AE1" s="1" t="s">
+      <c r="AF1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="AF1" s="1" t="s">
+      <c r="AG1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="AG1" s="1" t="s">
+      <c r="AH1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="AH1" s="1" t="s">
+      <c r="AI1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="AI1" s="1" t="s">
+      <c r="AJ1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="AJ1" s="1" t="s">
+      <c r="AK1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="AK1" s="1" t="s">
+      <c r="AL1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="AL1" s="1" t="s">
+      <c r="AM1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="AM1" s="1" t="s">
+      <c r="AN1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="AN1" s="1" t="s">
+      <c r="AO1" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="AO1" s="1" t="s">
+      <c r="AP1" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="AP1" s="1" t="s">
+      <c r="AQ1" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="AQ1" s="1" t="s">
+      <c r="AR1" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="AR1" s="1" t="s">
+      <c r="AS1" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="AS1" s="1" t="s">
+      <c r="AT1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="AT1" s="1" t="s">
+      <c r="AU1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="AU1" s="1" t="s">
+      <c r="AV1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="AV1" s="1" t="s">
+      <c r="AW1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AW1" s="1" t="s">
+      <c r="AX1" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="AX1" s="1" t="s">
+      <c r="AY1" s="1" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:50" x14ac:dyDescent="0.2">
-      <c r="AE2" s="2"/>
+    <row r="2" spans="1:51" x14ac:dyDescent="0.2">
       <c r="AF2" s="2"/>
       <c r="AG2" s="2"/>
       <c r="AH2" s="2"/>
+      <c r="AI2" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>

--- a/src/src/main/webapp/portal/wo/woExport/APM_WorkOrder_Template.xlsx
+++ b/src/src/main/webapp/portal/wo/woExport/APM_WorkOrder_Template.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20730"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F01B7AA2-8947-4A72-A424-B2216EE1FFF8}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03A0532B-0258-4858-ADCC-2AA89A499077}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7530" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="62">
   <si>
     <t>报修单号</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -264,6 +264,10 @@
   </si>
   <si>
     <t>报修人电话</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>属性</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -606,7 +610,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AZ2"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="4" width="20.5" customWidth="1"/>
@@ -637,9 +641,10 @@
     <col min="47" max="48" width="16.125" customWidth="1"/>
     <col min="49" max="49" width="9.375" customWidth="1"/>
     <col min="50" max="50" width="12.5" customWidth="1"/>
+    <col min="52" max="52" width="23.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:51" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:52" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -793,8 +798,11 @@
       <c r="AY1" s="1" t="s">
         <v>24</v>
       </c>
+      <c r="AZ1" s="1" t="s">
+        <v>61</v>
+      </c>
     </row>
-    <row r="2" spans="1:51" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:52" x14ac:dyDescent="0.2">
       <c r="AF2" s="2"/>
       <c r="AG2" s="2"/>
       <c r="AH2" s="2"/>

--- a/src/src/main/webapp/portal/wo/woExport/APM_WorkOrder_Template.xlsx
+++ b/src/src/main/webapp/portal/wo/woExport/APM_WorkOrder_Template.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="21929"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03A0532B-0258-4858-ADCC-2AA89A499077}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{249698C1-8C69-4317-849D-B2B899439D41}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="44" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7530" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12552" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="WorkOrder List" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="63">
   <si>
     <t>报修单号</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -269,17 +269,20 @@
   <si>
     <t>属性</t>
     <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>维修价值</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -292,7 +295,7 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="等线"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -300,7 +303,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -610,41 +613,41 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AZ2"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:BA2"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="4" width="20.5" customWidth="1"/>
-    <col min="5" max="6" width="23.125" customWidth="1"/>
-    <col min="7" max="7" width="16.375" customWidth="1"/>
-    <col min="8" max="17" width="17.5" customWidth="1"/>
-    <col min="18" max="18" width="20.375" customWidth="1"/>
-    <col min="19" max="20" width="16.25" customWidth="1"/>
-    <col min="21" max="21" width="15.875" customWidth="1"/>
-    <col min="22" max="22" width="25.375" customWidth="1"/>
+    <col min="2" max="4" width="20.47265625" customWidth="1"/>
+    <col min="5" max="6" width="23.1015625" customWidth="1"/>
+    <col min="7" max="7" width="16.3671875" customWidth="1"/>
+    <col min="8" max="17" width="17.47265625" customWidth="1"/>
+    <col min="18" max="18" width="20.3671875" customWidth="1"/>
+    <col min="19" max="20" width="16.26171875" customWidth="1"/>
+    <col min="21" max="21" width="15.89453125" customWidth="1"/>
+    <col min="22" max="22" width="25.3671875" customWidth="1"/>
     <col min="23" max="23" width="23" customWidth="1"/>
-    <col min="24" max="24" width="14.125" customWidth="1"/>
-    <col min="25" max="25" width="14.625" customWidth="1"/>
-    <col min="26" max="26" width="26.125" customWidth="1"/>
+    <col min="24" max="24" width="14.1015625" customWidth="1"/>
+    <col min="25" max="25" width="14.62890625" customWidth="1"/>
+    <col min="26" max="26" width="26.1015625" customWidth="1"/>
     <col min="27" max="27" width="25" customWidth="1"/>
-    <col min="28" max="30" width="16.375" customWidth="1"/>
-    <col min="31" max="31" width="12.25" customWidth="1"/>
+    <col min="28" max="30" width="16.3671875" customWidth="1"/>
+    <col min="31" max="31" width="12.26171875" customWidth="1"/>
     <col min="32" max="32" width="25" customWidth="1"/>
-    <col min="33" max="33" width="12.5" customWidth="1"/>
-    <col min="34" max="35" width="10.625" customWidth="1"/>
-    <col min="36" max="36" width="12.125" customWidth="1"/>
-    <col min="38" max="38" width="23.625" customWidth="1"/>
-    <col min="39" max="40" width="25.875" customWidth="1"/>
-    <col min="41" max="41" width="21" customWidth="1"/>
-    <col min="42" max="44" width="25.875" customWidth="1"/>
-    <col min="45" max="45" width="16.25" customWidth="1"/>
-    <col min="46" max="46" width="17" customWidth="1"/>
-    <col min="47" max="48" width="16.125" customWidth="1"/>
-    <col min="49" max="49" width="9.375" customWidth="1"/>
-    <col min="50" max="50" width="12.5" customWidth="1"/>
-    <col min="52" max="52" width="23.875" customWidth="1"/>
+    <col min="33" max="33" width="12.47265625" customWidth="1"/>
+    <col min="34" max="35" width="10.62890625" customWidth="1"/>
+    <col min="36" max="37" width="11.9453125" customWidth="1"/>
+    <col min="39" max="39" width="23.62890625" customWidth="1"/>
+    <col min="40" max="41" width="25.89453125" customWidth="1"/>
+    <col min="42" max="42" width="21" customWidth="1"/>
+    <col min="43" max="45" width="25.89453125" customWidth="1"/>
+    <col min="46" max="46" width="16.26171875" customWidth="1"/>
+    <col min="47" max="47" width="17" customWidth="1"/>
+    <col min="48" max="49" width="16.1015625" customWidth="1"/>
+    <col min="50" max="50" width="9.3671875" customWidth="1"/>
+    <col min="51" max="51" width="12.47265625" customWidth="1"/>
+    <col min="53" max="53" width="23.89453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:52" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:53" ht="15.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -754,55 +757,58 @@
         <v>27</v>
       </c>
       <c r="AK1" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="AL1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="AL1" s="1" t="s">
+      <c r="AM1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="AM1" s="1" t="s">
+      <c r="AN1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="AN1" s="1" t="s">
+      <c r="AO1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="AO1" s="1" t="s">
+      <c r="AP1" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="AP1" s="1" t="s">
+      <c r="AQ1" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="AQ1" s="1" t="s">
+      <c r="AR1" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="AR1" s="1" t="s">
+      <c r="AS1" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="AS1" s="1" t="s">
+      <c r="AT1" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="AT1" s="1" t="s">
+      <c r="AU1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="AU1" s="1" t="s">
+      <c r="AV1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="AV1" s="1" t="s">
+      <c r="AW1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="AW1" s="1" t="s">
+      <c r="AX1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AX1" s="1" t="s">
+      <c r="AY1" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="AY1" s="1" t="s">
+      <c r="AZ1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="AZ1" s="1" t="s">
+      <c r="BA1" s="1" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="2" spans="1:52" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:53">
       <c r="AF2" s="2"/>
       <c r="AG2" s="2"/>
       <c r="AH2" s="2"/>
@@ -818,12 +824,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{71B27B56-1823-4D07-9234-02F082420C5C}">
   <dimension ref="A1:L1"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="3" max="3" width="10.875" customWidth="1"/>
+    <col min="3" max="3" width="10.89453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:12">
       <c r="A1" t="s">
         <v>0</v>
       </c>

--- a/src/src/main/webapp/portal/wo/woExport/APM_WorkOrder_Template.xlsx
+++ b/src/src/main/webapp/portal/wo/woExport/APM_WorkOrder_Template.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="21929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10509"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{249698C1-8C69-4317-849D-B2B899439D41}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="44" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BACAA813-2969-A940-8769-51CF0DF10313}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="44" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12552" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="460" windowWidth="23240" windowHeight="12560" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="WorkOrder List" sheetId="1" r:id="rId1"/>
@@ -155,14 +155,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>协助者</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>协助者工时</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>品牌</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -272,6 +264,12 @@
   </si>
   <si>
     <t>维修价值</t>
+  </si>
+  <si>
+    <t>协作者</t>
+  </si>
+  <si>
+    <t>协作者工时</t>
   </si>
 </sst>
 </file>
@@ -614,40 +612,40 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:BA2"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="4" width="20.47265625" customWidth="1"/>
-    <col min="5" max="6" width="23.1015625" customWidth="1"/>
-    <col min="7" max="7" width="16.3671875" customWidth="1"/>
-    <col min="8" max="17" width="17.47265625" customWidth="1"/>
-    <col min="18" max="18" width="20.3671875" customWidth="1"/>
-    <col min="19" max="20" width="16.26171875" customWidth="1"/>
-    <col min="21" max="21" width="15.89453125" customWidth="1"/>
-    <col min="22" max="22" width="25.3671875" customWidth="1"/>
+    <col min="2" max="4" width="20.5" customWidth="1"/>
+    <col min="5" max="6" width="23.1640625" customWidth="1"/>
+    <col min="7" max="7" width="16.33203125" customWidth="1"/>
+    <col min="8" max="17" width="17.5" customWidth="1"/>
+    <col min="18" max="18" width="20.33203125" customWidth="1"/>
+    <col min="19" max="20" width="16.33203125" customWidth="1"/>
+    <col min="21" max="21" width="15.83203125" customWidth="1"/>
+    <col min="22" max="22" width="25.33203125" customWidth="1"/>
     <col min="23" max="23" width="23" customWidth="1"/>
-    <col min="24" max="24" width="14.1015625" customWidth="1"/>
-    <col min="25" max="25" width="14.62890625" customWidth="1"/>
-    <col min="26" max="26" width="26.1015625" customWidth="1"/>
+    <col min="24" max="24" width="14.1640625" customWidth="1"/>
+    <col min="25" max="25" width="14.6640625" customWidth="1"/>
+    <col min="26" max="26" width="26.1640625" customWidth="1"/>
     <col min="27" max="27" width="25" customWidth="1"/>
-    <col min="28" max="30" width="16.3671875" customWidth="1"/>
-    <col min="31" max="31" width="12.26171875" customWidth="1"/>
+    <col min="28" max="30" width="16.33203125" customWidth="1"/>
+    <col min="31" max="31" width="12.33203125" customWidth="1"/>
     <col min="32" max="32" width="25" customWidth="1"/>
-    <col min="33" max="33" width="12.47265625" customWidth="1"/>
-    <col min="34" max="35" width="10.62890625" customWidth="1"/>
-    <col min="36" max="37" width="11.9453125" customWidth="1"/>
-    <col min="39" max="39" width="23.62890625" customWidth="1"/>
-    <col min="40" max="41" width="25.89453125" customWidth="1"/>
+    <col min="33" max="33" width="12.5" customWidth="1"/>
+    <col min="34" max="35" width="10.6640625" customWidth="1"/>
+    <col min="36" max="37" width="12" customWidth="1"/>
+    <col min="39" max="39" width="23.6640625" customWidth="1"/>
+    <col min="40" max="41" width="25.83203125" customWidth="1"/>
     <col min="42" max="42" width="21" customWidth="1"/>
-    <col min="43" max="45" width="25.89453125" customWidth="1"/>
-    <col min="46" max="46" width="16.26171875" customWidth="1"/>
+    <col min="43" max="45" width="25.83203125" customWidth="1"/>
+    <col min="46" max="46" width="16.33203125" customWidth="1"/>
     <col min="47" max="47" width="17" customWidth="1"/>
-    <col min="48" max="49" width="16.1015625" customWidth="1"/>
-    <col min="50" max="50" width="9.3671875" customWidth="1"/>
-    <col min="51" max="51" width="12.47265625" customWidth="1"/>
-    <col min="53" max="53" width="23.89453125" customWidth="1"/>
+    <col min="48" max="49" width="16.1640625" customWidth="1"/>
+    <col min="50" max="50" width="9.33203125" customWidth="1"/>
+    <col min="51" max="51" width="12.5" customWidth="1"/>
+    <col min="53" max="53" width="23.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:53" ht="15.3">
+    <row r="1" spans="1:53" ht="17">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -658,7 +656,7 @@
         <v>21</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>2</v>
@@ -673,25 +671,25 @@
         <v>4</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="K1" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="M1" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>41</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>43</v>
       </c>
       <c r="P1" s="1" t="s">
         <v>23</v>
@@ -706,7 +704,7 @@
         <v>6</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="U1" s="1" t="s">
         <v>7</v>
@@ -721,7 +719,7 @@
         <v>10</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="Z1" s="1" t="s">
         <v>11</v>
@@ -733,13 +731,13 @@
         <v>13</v>
       </c>
       <c r="AC1" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AD1" s="1" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="AE1" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AF1" s="1" t="s">
         <v>14</v>
@@ -757,7 +755,7 @@
         <v>27</v>
       </c>
       <c r="AK1" s="1" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="AL1" s="1" t="s">
         <v>20</v>
@@ -772,19 +770,19 @@
         <v>17</v>
       </c>
       <c r="AP1" s="1" t="s">
-        <v>33</v>
+        <v>61</v>
       </c>
       <c r="AQ1" s="1" t="s">
-        <v>34</v>
+        <v>62</v>
       </c>
       <c r="AR1" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AS1" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="AT1" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="AU1" s="1" t="s">
         <v>18</v>
@@ -805,7 +803,7 @@
         <v>24</v>
       </c>
       <c r="BA1" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="2" spans="1:53">
@@ -824,9 +822,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{71B27B56-1823-4D07-9234-02F082420C5C}">
   <dimension ref="A1:L1"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col min="3" max="3" width="10.89453125" customWidth="1"/>
+    <col min="3" max="3" width="10.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12">
@@ -834,34 +832,34 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C1" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E1" t="s">
+        <v>55</v>
+      </c>
+      <c r="F1" t="s">
+        <v>47</v>
+      </c>
+      <c r="G1" t="s">
         <v>48</v>
       </c>
-      <c r="E1" t="s">
-        <v>57</v>
-      </c>
-      <c r="F1" t="s">
+      <c r="H1" t="s">
         <v>49</v>
       </c>
-      <c r="G1" t="s">
+      <c r="I1" t="s">
         <v>50</v>
       </c>
-      <c r="H1" t="s">
+      <c r="J1" t="s">
         <v>51</v>
       </c>
-      <c r="I1" t="s">
+      <c r="K1" t="s">
         <v>52</v>
-      </c>
-      <c r="J1" t="s">
-        <v>53</v>
-      </c>
-      <c r="K1" t="s">
-        <v>54</v>
       </c>
       <c r="L1" t="s">
         <v>24</v>

--- a/src/src/main/webapp/portal/wo/woExport/APM_WorkOrder_Template.xlsx
+++ b/src/src/main/webapp/portal/wo/woExport/APM_WorkOrder_Template.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10509"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="22527"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BACAA813-2969-A940-8769-51CF0DF10313}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="44" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEBA5280-F769-4EE6-9E6C-8C9A2ECB23E8}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="460" windowWidth="23240" windowHeight="12560" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12552" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="WorkOrder List" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="64">
   <si>
     <t>报修单号</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -235,41 +235,43 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
+    <t>修复后无故障天数</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>合同价格</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>设备编号</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>资产名称</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>报修人电话</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>属性</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>维修价值</t>
+  </si>
+  <si>
+    <t>协作者</t>
+  </si>
+  <si>
+    <t>协作者工时</t>
+  </si>
+  <si>
     <t>维修类型</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>修复后无故障天数</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>合同价格</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>设备编号</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>资产名称</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>报修人电话</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>属性</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>维修价值</t>
-  </si>
-  <si>
-    <t>协作者</t>
-  </si>
-  <si>
-    <t>协作者工时</t>
+  </si>
+  <si>
+    <t>维修结果</t>
   </si>
 </sst>
 </file>
@@ -333,7 +335,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -611,41 +613,41 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:BA2"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <dimension ref="A1:BB2"/>
+  <sheetFormatPr defaultColWidth="8.83984375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="4" width="20.5" customWidth="1"/>
-    <col min="5" max="6" width="23.1640625" customWidth="1"/>
-    <col min="7" max="7" width="16.33203125" customWidth="1"/>
-    <col min="8" max="17" width="17.5" customWidth="1"/>
-    <col min="18" max="18" width="20.33203125" customWidth="1"/>
-    <col min="19" max="20" width="16.33203125" customWidth="1"/>
-    <col min="21" max="21" width="15.83203125" customWidth="1"/>
-    <col min="22" max="22" width="25.33203125" customWidth="1"/>
+    <col min="2" max="4" width="20.47265625" customWidth="1"/>
+    <col min="5" max="6" width="23.15625" customWidth="1"/>
+    <col min="7" max="7" width="16.3125" customWidth="1"/>
+    <col min="8" max="17" width="17.47265625" customWidth="1"/>
+    <col min="18" max="18" width="20.3125" customWidth="1"/>
+    <col min="19" max="20" width="16.3125" customWidth="1"/>
+    <col min="21" max="21" width="15.83984375" customWidth="1"/>
+    <col min="22" max="22" width="25.3125" customWidth="1"/>
     <col min="23" max="23" width="23" customWidth="1"/>
-    <col min="24" max="24" width="14.1640625" customWidth="1"/>
-    <col min="25" max="25" width="14.6640625" customWidth="1"/>
-    <col min="26" max="26" width="26.1640625" customWidth="1"/>
-    <col min="27" max="27" width="25" customWidth="1"/>
-    <col min="28" max="30" width="16.33203125" customWidth="1"/>
-    <col min="31" max="31" width="12.33203125" customWidth="1"/>
-    <col min="32" max="32" width="25" customWidth="1"/>
-    <col min="33" max="33" width="12.5" customWidth="1"/>
-    <col min="34" max="35" width="10.6640625" customWidth="1"/>
-    <col min="36" max="37" width="12" customWidth="1"/>
-    <col min="39" max="39" width="23.6640625" customWidth="1"/>
-    <col min="40" max="41" width="25.83203125" customWidth="1"/>
-    <col min="42" max="42" width="21" customWidth="1"/>
-    <col min="43" max="45" width="25.83203125" customWidth="1"/>
-    <col min="46" max="46" width="16.33203125" customWidth="1"/>
-    <col min="47" max="47" width="17" customWidth="1"/>
-    <col min="48" max="49" width="16.1640625" customWidth="1"/>
-    <col min="50" max="50" width="9.33203125" customWidth="1"/>
-    <col min="51" max="51" width="12.5" customWidth="1"/>
-    <col min="53" max="53" width="23.83203125" customWidth="1"/>
+    <col min="24" max="25" width="14.15625" customWidth="1"/>
+    <col min="26" max="26" width="14.68359375" customWidth="1"/>
+    <col min="27" max="27" width="26.15625" customWidth="1"/>
+    <col min="28" max="28" width="25" customWidth="1"/>
+    <col min="29" max="31" width="16.3125" customWidth="1"/>
+    <col min="32" max="32" width="12.3125" customWidth="1"/>
+    <col min="33" max="33" width="25" customWidth="1"/>
+    <col min="34" max="34" width="12.47265625" customWidth="1"/>
+    <col min="35" max="36" width="10.68359375" customWidth="1"/>
+    <col min="37" max="38" width="12" customWidth="1"/>
+    <col min="40" max="40" width="23.68359375" customWidth="1"/>
+    <col min="41" max="42" width="25.83984375" customWidth="1"/>
+    <col min="43" max="43" width="21" customWidth="1"/>
+    <col min="44" max="46" width="25.83984375" customWidth="1"/>
+    <col min="47" max="47" width="16.3125" customWidth="1"/>
+    <col min="48" max="48" width="17" customWidth="1"/>
+    <col min="49" max="50" width="16.15625" customWidth="1"/>
+    <col min="51" max="51" width="9.3125" customWidth="1"/>
+    <col min="52" max="52" width="12.47265625" customWidth="1"/>
+    <col min="54" max="54" width="23.83984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:53" ht="17">
+    <row r="1" spans="1:54" ht="15.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -704,7 +706,7 @@
         <v>6</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="U1" s="1" t="s">
         <v>7</v>
@@ -719,98 +721,101 @@
         <v>10</v>
       </c>
       <c r="Y1" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="AA1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="AB1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="AC1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AD1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AE1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="AF1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="AG1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="AH1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="AI1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AJ1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="AK1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AL1" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="AM1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="AN1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="AO1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="AP1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="AQ1" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="AR1" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="AS1" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="AT1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="AU1" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="Z1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="AA1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="AB1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="AC1" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="AD1" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="AE1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="AF1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="AG1" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="AH1" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="AI1" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="AJ1" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="AK1" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="AL1" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="AM1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="AN1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="AO1" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="AP1" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="AQ1" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="AR1" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="AS1" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="AT1" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="AU1" s="1" t="s">
+      <c r="AV1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="AV1" s="1" t="s">
+      <c r="AW1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="AW1" s="1" t="s">
+      <c r="AX1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="AX1" s="1" t="s">
+      <c r="AY1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AY1" s="1" t="s">
+      <c r="AZ1" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="AZ1" s="1" t="s">
+      <c r="BA1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="BA1" s="1" t="s">
-        <v>59</v>
+      <c r="BB1" s="1" t="s">
+        <v>58</v>
       </c>
     </row>
-    <row r="2" spans="1:53">
-      <c r="AF2" s="2"/>
+    <row r="2" spans="1:54">
       <c r="AG2" s="2"/>
       <c r="AH2" s="2"/>
       <c r="AI2" s="2"/>
+      <c r="AJ2" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
@@ -822,9 +827,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{71B27B56-1823-4D07-9234-02F082420C5C}">
   <dimension ref="A1:L1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.83984375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="3" max="3" width="10.83203125" customWidth="1"/>
+    <col min="3" max="3" width="10.83984375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12">
@@ -832,16 +837,16 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D1" t="s">
         <v>46</v>
       </c>
       <c r="E1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F1" t="s">
         <v>47</v>

--- a/src/src/main/webapp/portal/wo/woExport/APM_WorkOrder_Template.xlsx
+++ b/src/src/main/webapp/portal/wo/woExport/APM_WorkOrder_Template.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="22527"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="23127"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEBA5280-F769-4EE6-9E6C-8C9A2ECB23E8}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE61C795-B7A3-4E0D-ACC3-29AD6F3EAFF8}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12552" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="WorkOrder List" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="65">
   <si>
     <t>报修单号</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -272,6 +272,9 @@
   </si>
   <si>
     <t>维修结果</t>
+  </si>
+  <si>
+    <t>维修子状态</t>
   </si>
 </sst>
 </file>
@@ -335,7 +338,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -613,7 +616,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:BB2"/>
+  <dimension ref="A1:BC2"/>
   <sheetFormatPr defaultColWidth="8.83984375" defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="4" width="20.47265625" customWidth="1"/>
@@ -625,29 +628,29 @@
     <col min="21" max="21" width="15.83984375" customWidth="1"/>
     <col min="22" max="22" width="25.3125" customWidth="1"/>
     <col min="23" max="23" width="23" customWidth="1"/>
-    <col min="24" max="25" width="14.15625" customWidth="1"/>
-    <col min="26" max="26" width="14.68359375" customWidth="1"/>
-    <col min="27" max="27" width="26.15625" customWidth="1"/>
-    <col min="28" max="28" width="25" customWidth="1"/>
-    <col min="29" max="31" width="16.3125" customWidth="1"/>
-    <col min="32" max="32" width="12.3125" customWidth="1"/>
-    <col min="33" max="33" width="25" customWidth="1"/>
-    <col min="34" max="34" width="12.47265625" customWidth="1"/>
-    <col min="35" max="36" width="10.68359375" customWidth="1"/>
-    <col min="37" max="38" width="12" customWidth="1"/>
-    <col min="40" max="40" width="23.68359375" customWidth="1"/>
-    <col min="41" max="42" width="25.83984375" customWidth="1"/>
-    <col min="43" max="43" width="21" customWidth="1"/>
-    <col min="44" max="46" width="25.83984375" customWidth="1"/>
-    <col min="47" max="47" width="16.3125" customWidth="1"/>
-    <col min="48" max="48" width="17" customWidth="1"/>
-    <col min="49" max="50" width="16.15625" customWidth="1"/>
-    <col min="51" max="51" width="9.3125" customWidth="1"/>
-    <col min="52" max="52" width="12.47265625" customWidth="1"/>
-    <col min="54" max="54" width="23.83984375" customWidth="1"/>
+    <col min="24" max="26" width="14.15625" customWidth="1"/>
+    <col min="27" max="27" width="14.68359375" customWidth="1"/>
+    <col min="28" max="28" width="26.15625" customWidth="1"/>
+    <col min="29" max="29" width="25" customWidth="1"/>
+    <col min="30" max="32" width="16.3125" customWidth="1"/>
+    <col min="33" max="33" width="12.3125" customWidth="1"/>
+    <col min="34" max="34" width="25" customWidth="1"/>
+    <col min="35" max="35" width="12.47265625" customWidth="1"/>
+    <col min="36" max="37" width="10.68359375" customWidth="1"/>
+    <col min="38" max="39" width="12" customWidth="1"/>
+    <col min="41" max="41" width="23.68359375" customWidth="1"/>
+    <col min="42" max="43" width="25.83984375" customWidth="1"/>
+    <col min="44" max="44" width="21" customWidth="1"/>
+    <col min="45" max="47" width="25.83984375" customWidth="1"/>
+    <col min="48" max="48" width="16.3125" customWidth="1"/>
+    <col min="49" max="49" width="17" customWidth="1"/>
+    <col min="50" max="51" width="16.15625" customWidth="1"/>
+    <col min="52" max="52" width="9.3125" customWidth="1"/>
+    <col min="53" max="53" width="12.47265625" customWidth="1"/>
+    <col min="55" max="55" width="23.83984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:54" ht="15.3">
+    <row r="1" spans="1:55" ht="15.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -724,98 +727,101 @@
         <v>62</v>
       </c>
       <c r="Z1" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="AA1" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="AA1" s="1" t="s">
+      <c r="AB1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="AB1" s="1" t="s">
+      <c r="AC1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="AC1" s="1" t="s">
+      <c r="AD1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="AD1" s="1" t="s">
+      <c r="AE1" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE1" s="1" t="s">
+      <c r="AF1" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="AF1" s="1" t="s">
+      <c r="AG1" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="AG1" s="1" t="s">
+      <c r="AH1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="AH1" s="1" t="s">
+      <c r="AI1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="AI1" s="1" t="s">
+      <c r="AJ1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="AJ1" s="1" t="s">
+      <c r="AK1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="AK1" s="1" t="s">
+      <c r="AL1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="AL1" s="1" t="s">
+      <c r="AM1" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="AM1" s="1" t="s">
+      <c r="AN1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="AN1" s="1" t="s">
+      <c r="AO1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="AO1" s="1" t="s">
+      <c r="AP1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="AP1" s="1" t="s">
+      <c r="AQ1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="AQ1" s="1" t="s">
+      <c r="AR1" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="AR1" s="1" t="s">
+      <c r="AS1" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="AS1" s="1" t="s">
+      <c r="AT1" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="AT1" s="1" t="s">
+      <c r="AU1" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="AU1" s="1" t="s">
+      <c r="AV1" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="AV1" s="1" t="s">
+      <c r="AW1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="AW1" s="1" t="s">
+      <c r="AX1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="AX1" s="1" t="s">
+      <c r="AY1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="AY1" s="1" t="s">
+      <c r="AZ1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AZ1" s="1" t="s">
+      <c r="BA1" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="BA1" s="1" t="s">
+      <c r="BB1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="BB1" s="1" t="s">
+      <c r="BC1" s="1" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="2" spans="1:54">
-      <c r="AG2" s="2"/>
+    <row r="2" spans="1:55">
       <c r="AH2" s="2"/>
       <c r="AI2" s="2"/>
       <c r="AJ2" s="2"/>
+      <c r="AK2" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>

--- a/src/src/main/webapp/portal/wo/woExport/APM_WorkOrder_Template.xlsx
+++ b/src/src/main/webapp/portal/wo/woExport/APM_WorkOrder_Template.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="23127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="23801"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE61C795-B7A3-4E0D-ACC3-29AD6F3EAFF8}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EE4427A-E930-4177-A2DC-8CBFC470AD03}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13152" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="WorkOrder List" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="66">
   <si>
     <t>报修单号</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -275,6 +275,9 @@
   </si>
   <si>
     <t>维修子状态</t>
+  </si>
+  <si>
+    <t>是否MVS工单</t>
   </si>
 </sst>
 </file>
@@ -616,7 +619,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:BC2"/>
+  <dimension ref="A1:BD2"/>
   <sheetFormatPr defaultColWidth="8.83984375" defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="4" width="20.47265625" customWidth="1"/>
@@ -648,9 +651,10 @@
     <col min="52" max="52" width="9.3125" customWidth="1"/>
     <col min="53" max="53" width="12.47265625" customWidth="1"/>
     <col min="55" max="55" width="23.83984375" customWidth="1"/>
+    <col min="56" max="56" width="15.5234375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:55" ht="15.3">
+    <row r="1" spans="1:56" ht="15.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -816,8 +820,11 @@
       <c r="BC1" s="1" t="s">
         <v>58</v>
       </c>
+      <c r="BD1" s="1" t="s">
+        <v>65</v>
+      </c>
     </row>
-    <row r="2" spans="1:55">
+    <row r="2" spans="1:56">
       <c r="AH2" s="2"/>
       <c r="AI2" s="2"/>
       <c r="AJ2" s="2"/>

--- a/src/src/main/webapp/portal/wo/woExport/APM_WorkOrder_Template.xlsx
+++ b/src/src/main/webapp/portal/wo/woExport/APM_WorkOrder_Template.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="23801"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24326"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EE4427A-E930-4177-A2DC-8CBFC470AD03}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC20127E-0DA7-47D0-9FDE-D77ED1549B4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13152" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView minimized="1" xWindow="336" yWindow="2928" windowWidth="22704" windowHeight="8994" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="WorkOrder List" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="68">
   <si>
     <t>报修单号</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -277,7 +277,16 @@
     <t>维修子状态</t>
   </si>
   <si>
+    <t>sieble单号</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>呼叫中心单号</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
     <t>是否MVS工单</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -288,7 +297,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="等线"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -301,7 +310,7 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="Calibri"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -309,7 +318,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -341,7 +350,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -619,42 +628,44 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:BD2"/>
-  <sheetFormatPr defaultColWidth="8.83984375" defaultRowHeight="14.4"/>
+  <dimension ref="A1:BF2"/>
+  <sheetFormatPr defaultColWidth="8.84765625" defaultRowHeight="14.1"/>
   <cols>
-    <col min="2" max="4" width="20.47265625" customWidth="1"/>
-    <col min="5" max="6" width="23.15625" customWidth="1"/>
-    <col min="7" max="7" width="16.3125" customWidth="1"/>
-    <col min="8" max="17" width="17.47265625" customWidth="1"/>
-    <col min="18" max="18" width="20.3125" customWidth="1"/>
-    <col min="19" max="20" width="16.3125" customWidth="1"/>
-    <col min="21" max="21" width="15.83984375" customWidth="1"/>
-    <col min="22" max="22" width="25.3125" customWidth="1"/>
+    <col min="2" max="4" width="20.44921875" customWidth="1"/>
+    <col min="5" max="6" width="23.1484375" customWidth="1"/>
+    <col min="7" max="7" width="16.296875" customWidth="1"/>
+    <col min="8" max="17" width="17.44921875" customWidth="1"/>
+    <col min="18" max="18" width="20.296875" customWidth="1"/>
+    <col min="19" max="20" width="16.296875" customWidth="1"/>
+    <col min="21" max="21" width="15.84765625" customWidth="1"/>
+    <col min="22" max="22" width="25.296875" customWidth="1"/>
     <col min="23" max="23" width="23" customWidth="1"/>
-    <col min="24" max="26" width="14.15625" customWidth="1"/>
-    <col min="27" max="27" width="14.68359375" customWidth="1"/>
-    <col min="28" max="28" width="26.15625" customWidth="1"/>
+    <col min="24" max="26" width="14.1484375" customWidth="1"/>
+    <col min="27" max="27" width="14.69921875" customWidth="1"/>
+    <col min="28" max="28" width="26.1484375" customWidth="1"/>
     <col min="29" max="29" width="25" customWidth="1"/>
-    <col min="30" max="32" width="16.3125" customWidth="1"/>
-    <col min="33" max="33" width="12.3125" customWidth="1"/>
+    <col min="30" max="32" width="16.296875" customWidth="1"/>
+    <col min="33" max="33" width="12.296875" customWidth="1"/>
     <col min="34" max="34" width="25" customWidth="1"/>
-    <col min="35" max="35" width="12.47265625" customWidth="1"/>
-    <col min="36" max="37" width="10.68359375" customWidth="1"/>
+    <col min="35" max="35" width="12.44921875" customWidth="1"/>
+    <col min="36" max="37" width="10.69921875" customWidth="1"/>
     <col min="38" max="39" width="12" customWidth="1"/>
-    <col min="41" max="41" width="23.68359375" customWidth="1"/>
-    <col min="42" max="43" width="25.83984375" customWidth="1"/>
+    <col min="41" max="41" width="23.69921875" customWidth="1"/>
+    <col min="42" max="43" width="25.84765625" customWidth="1"/>
     <col min="44" max="44" width="21" customWidth="1"/>
-    <col min="45" max="47" width="25.83984375" customWidth="1"/>
-    <col min="48" max="48" width="16.3125" customWidth="1"/>
+    <col min="45" max="47" width="25.84765625" customWidth="1"/>
+    <col min="48" max="48" width="16.296875" customWidth="1"/>
     <col min="49" max="49" width="17" customWidth="1"/>
-    <col min="50" max="51" width="16.15625" customWidth="1"/>
-    <col min="52" max="52" width="9.3125" customWidth="1"/>
-    <col min="53" max="53" width="12.47265625" customWidth="1"/>
-    <col min="55" max="55" width="23.83984375" customWidth="1"/>
-    <col min="56" max="56" width="15.5234375" customWidth="1"/>
+    <col min="50" max="51" width="16.1484375" customWidth="1"/>
+    <col min="52" max="52" width="9.296875" customWidth="1"/>
+    <col min="53" max="53" width="12.44921875" customWidth="1"/>
+    <col min="55" max="55" width="23.84765625" customWidth="1"/>
+    <col min="56" max="56" width="15.5" customWidth="1"/>
+    <col min="57" max="57" width="11.25" customWidth="1"/>
+    <col min="58" max="58" width="10.296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:56" ht="15.3">
+    <row r="1" spans="1:58" ht="15.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -821,10 +832,16 @@
         <v>58</v>
       </c>
       <c r="BD1" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="BE1" s="1" t="s">
         <v>65</v>
       </c>
+      <c r="BF1" s="1" t="s">
+        <v>66</v>
+      </c>
     </row>
-    <row r="2" spans="1:56">
+    <row r="2" spans="1:58">
       <c r="AH2" s="2"/>
       <c r="AI2" s="2"/>
       <c r="AJ2" s="2"/>
@@ -840,9 +857,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{71B27B56-1823-4D07-9234-02F082420C5C}">
   <dimension ref="A1:L1"/>
-  <sheetFormatPr defaultColWidth="8.83984375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.84765625" defaultRowHeight="14.1"/>
   <cols>
-    <col min="3" max="3" width="10.83984375" customWidth="1"/>
+    <col min="3" max="3" width="10.84765625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12">

--- a/src/src/main/webapp/portal/wo/woExport/APM_WorkOrder_Template.xlsx
+++ b/src/src/main/webapp/portal/wo/woExport/APM_WorkOrder_Template.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24326"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC20127E-0DA7-47D0-9FDE-D77ED1549B4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41B0047E-F640-4018-96E5-4B268FDFC0DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="336" yWindow="2928" windowWidth="22704" windowHeight="8994" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12552" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="WorkOrder List" sheetId="1" r:id="rId1"/>
@@ -662,7 +662,7 @@
     <col min="55" max="55" width="23.84765625" customWidth="1"/>
     <col min="56" max="56" width="15.5" customWidth="1"/>
     <col min="57" max="57" width="11.25" customWidth="1"/>
-    <col min="58" max="58" width="10.296875" customWidth="1"/>
+    <col min="58" max="58" width="12.09765625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:58" ht="15.3">

--- a/src/src/main/webapp/portal/wo/woExport/APM_WorkOrder_Template.xlsx
+++ b/src/src/main/webapp/portal/wo/woExport/APM_WorkOrder_Template.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24326"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41B0047E-F640-4018-96E5-4B268FDFC0DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BAE5E67-691E-4BB6-AD3C-B947F64F6B87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12552" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="336" yWindow="696" windowWidth="22704" windowHeight="10860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="WorkOrder List" sheetId="1" r:id="rId1"/>
@@ -277,15 +277,15 @@
     <t>维修子状态</t>
   </si>
   <si>
-    <t>sieble单号</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>呼叫中心单号</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>是否MVS工单</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>siebel单号</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -832,13 +832,13 @@
         <v>58</v>
       </c>
       <c r="BD1" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="BE1" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="BE1" s="1" t="s">
+      <c r="BF1" s="1" t="s">
         <v>65</v>
-      </c>
-      <c r="BF1" s="1" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="2" spans="1:58">

--- a/src/src/main/webapp/portal/wo/woExport/APM_WorkOrder_Template.xlsx
+++ b/src/src/main/webapp/portal/wo/woExport/APM_WorkOrder_Template.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24931"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BAE5E67-691E-4BB6-AD3C-B947F64F6B87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{603E47DD-EAEB-4C6E-850E-2E8144324585}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="336" yWindow="696" windowWidth="22704" windowHeight="10860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12552" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="WorkOrder List" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="70">
   <si>
     <t>报修单号</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -286,6 +286,14 @@
   </si>
   <si>
     <t>siebel单号</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>工时填写方式</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>维修工时详情</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -628,7 +636,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:BF2"/>
+  <dimension ref="A1:BH2"/>
   <sheetFormatPr defaultColWidth="8.84765625" defaultRowHeight="14.1"/>
   <cols>
     <col min="2" max="4" width="20.44921875" customWidth="1"/>
@@ -663,9 +671,10 @@
     <col min="56" max="56" width="15.5" customWidth="1"/>
     <col min="57" max="57" width="11.25" customWidth="1"/>
     <col min="58" max="58" width="12.09765625" customWidth="1"/>
+    <col min="59" max="60" width="12.19921875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:58" ht="15.3">
+    <row r="1" spans="1:60" ht="15.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -840,8 +849,14 @@
       <c r="BF1" s="1" t="s">
         <v>65</v>
       </c>
+      <c r="BG1" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="BH1" s="1" t="s">
+        <v>69</v>
+      </c>
     </row>
-    <row r="2" spans="1:58">
+    <row r="2" spans="1:60">
       <c r="AH2" s="2"/>
       <c r="AI2" s="2"/>
       <c r="AJ2" s="2"/>

--- a/src/src/main/webapp/portal/wo/woExport/APM_WorkOrder_Template.xlsx
+++ b/src/src/main/webapp/portal/wo/woExport/APM_WorkOrder_Template.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24931"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26130"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{603E47DD-EAEB-4C6E-850E-2E8144324585}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6D8EE15-1543-46A3-A16E-F5C3B34477CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12552" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-93" yWindow="-93" windowWidth="25786" windowHeight="13986" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="WorkOrder List" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="71">
   <si>
     <t>报修单号</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -294,6 +294,10 @@
   </si>
   <si>
     <t>维修工时详情</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>外部报价</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -301,7 +305,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -636,45 +640,45 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:BH2"/>
-  <sheetFormatPr defaultColWidth="8.84765625" defaultRowHeight="14.1"/>
+  <dimension ref="A1:BI2"/>
+  <sheetFormatPr defaultColWidth="8.8203125" defaultRowHeight="14" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="2" max="4" width="20.44921875" customWidth="1"/>
-    <col min="5" max="6" width="23.1484375" customWidth="1"/>
-    <col min="7" max="7" width="16.296875" customWidth="1"/>
-    <col min="8" max="17" width="17.44921875" customWidth="1"/>
-    <col min="18" max="18" width="20.296875" customWidth="1"/>
-    <col min="19" max="20" width="16.296875" customWidth="1"/>
-    <col min="21" max="21" width="15.84765625" customWidth="1"/>
-    <col min="22" max="22" width="25.296875" customWidth="1"/>
+    <col min="2" max="4" width="20.46875" customWidth="1"/>
+    <col min="5" max="6" width="23.1171875" customWidth="1"/>
+    <col min="7" max="7" width="16.29296875" customWidth="1"/>
+    <col min="8" max="17" width="17.46875" customWidth="1"/>
+    <col min="18" max="18" width="20.29296875" customWidth="1"/>
+    <col min="19" max="20" width="16.29296875" customWidth="1"/>
+    <col min="21" max="21" width="15.8203125" customWidth="1"/>
+    <col min="22" max="22" width="25.29296875" customWidth="1"/>
     <col min="23" max="23" width="23" customWidth="1"/>
-    <col min="24" max="26" width="14.1484375" customWidth="1"/>
-    <col min="27" max="27" width="14.69921875" customWidth="1"/>
-    <col min="28" max="28" width="26.1484375" customWidth="1"/>
+    <col min="24" max="26" width="14.1171875" customWidth="1"/>
+    <col min="27" max="27" width="14.703125" customWidth="1"/>
+    <col min="28" max="28" width="26.1171875" customWidth="1"/>
     <col min="29" max="29" width="25" customWidth="1"/>
-    <col min="30" max="32" width="16.296875" customWidth="1"/>
-    <col min="33" max="33" width="12.296875" customWidth="1"/>
+    <col min="30" max="32" width="16.29296875" customWidth="1"/>
+    <col min="33" max="33" width="12.29296875" customWidth="1"/>
     <col min="34" max="34" width="25" customWidth="1"/>
-    <col min="35" max="35" width="12.44921875" customWidth="1"/>
-    <col min="36" max="37" width="10.69921875" customWidth="1"/>
+    <col min="35" max="35" width="12.46875" customWidth="1"/>
+    <col min="36" max="37" width="10.703125" customWidth="1"/>
     <col min="38" max="39" width="12" customWidth="1"/>
-    <col min="41" max="41" width="23.69921875" customWidth="1"/>
-    <col min="42" max="43" width="25.84765625" customWidth="1"/>
+    <col min="41" max="41" width="23.703125" customWidth="1"/>
+    <col min="42" max="43" width="25.8203125" customWidth="1"/>
     <col min="44" max="44" width="21" customWidth="1"/>
-    <col min="45" max="47" width="25.84765625" customWidth="1"/>
-    <col min="48" max="48" width="16.296875" customWidth="1"/>
+    <col min="45" max="47" width="25.8203125" customWidth="1"/>
+    <col min="48" max="48" width="16.29296875" customWidth="1"/>
     <col min="49" max="49" width="17" customWidth="1"/>
-    <col min="50" max="51" width="16.1484375" customWidth="1"/>
-    <col min="52" max="52" width="9.296875" customWidth="1"/>
-    <col min="53" max="53" width="12.44921875" customWidth="1"/>
-    <col min="55" max="55" width="23.84765625" customWidth="1"/>
-    <col min="56" max="56" width="15.5" customWidth="1"/>
-    <col min="57" max="57" width="11.25" customWidth="1"/>
-    <col min="58" max="58" width="12.09765625" customWidth="1"/>
-    <col min="59" max="60" width="12.19921875" bestFit="1" customWidth="1"/>
+    <col min="50" max="51" width="16.1171875" customWidth="1"/>
+    <col min="52" max="52" width="9.29296875" customWidth="1"/>
+    <col min="53" max="53" width="12.46875" customWidth="1"/>
+    <col min="55" max="55" width="23.8203125" customWidth="1"/>
+    <col min="56" max="56" width="15.46875" customWidth="1"/>
+    <col min="57" max="57" width="11.234375" customWidth="1"/>
+    <col min="58" max="58" width="12.1171875" customWidth="1"/>
+    <col min="59" max="60" width="12.17578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:60" ht="15.3">
+    <row r="1" spans="1:61" ht="15.35" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -855,8 +859,11 @@
       <c r="BH1" s="1" t="s">
         <v>69</v>
       </c>
+      <c r="BI1" s="1" t="s">
+        <v>70</v>
+      </c>
     </row>
-    <row r="2" spans="1:60">
+    <row r="2" spans="1:61" x14ac:dyDescent="0.45">
       <c r="AH2" s="2"/>
       <c r="AI2" s="2"/>
       <c r="AJ2" s="2"/>
@@ -872,12 +879,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{71B27B56-1823-4D07-9234-02F082420C5C}">
   <dimension ref="A1:L1"/>
-  <sheetFormatPr defaultColWidth="8.84765625" defaultRowHeight="14.1"/>
+  <sheetFormatPr defaultColWidth="8.8203125" defaultRowHeight="14" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="3" max="3" width="10.84765625" customWidth="1"/>
+    <col min="3" max="3" width="10.8203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>0</v>
       </c>

--- a/src/src/main/webapp/portal/wo/woExport/APM_WorkOrder_Template.xlsx
+++ b/src/src/main/webapp/portal/wo/woExport/APM_WorkOrder_Template.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26130"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26924"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6D8EE15-1543-46A3-A16E-F5C3B34477CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD361C61-00A6-4BBD-BA79-D9264D1A06B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-93" yWindow="-93" windowWidth="25786" windowHeight="13986" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="WorkOrder List" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="72">
   <si>
     <t>报修单号</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -298,6 +298,10 @@
   </si>
   <si>
     <t>外部报价</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>备件类别</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -641,44 +645,44 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:BI2"/>
-  <sheetFormatPr defaultColWidth="8.8203125" defaultRowHeight="14" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="4" width="20.46875" customWidth="1"/>
-    <col min="5" max="6" width="23.1171875" customWidth="1"/>
-    <col min="7" max="7" width="16.29296875" customWidth="1"/>
-    <col min="8" max="17" width="17.46875" customWidth="1"/>
-    <col min="18" max="18" width="20.29296875" customWidth="1"/>
-    <col min="19" max="20" width="16.29296875" customWidth="1"/>
-    <col min="21" max="21" width="15.8203125" customWidth="1"/>
-    <col min="22" max="22" width="25.29296875" customWidth="1"/>
+    <col min="2" max="4" width="20.5" customWidth="1"/>
+    <col min="5" max="6" width="23.125" customWidth="1"/>
+    <col min="7" max="7" width="16.25" customWidth="1"/>
+    <col min="8" max="17" width="17.5" customWidth="1"/>
+    <col min="18" max="18" width="20.25" customWidth="1"/>
+    <col min="19" max="20" width="16.25" customWidth="1"/>
+    <col min="21" max="21" width="15.875" customWidth="1"/>
+    <col min="22" max="22" width="25.25" customWidth="1"/>
     <col min="23" max="23" width="23" customWidth="1"/>
-    <col min="24" max="26" width="14.1171875" customWidth="1"/>
-    <col min="27" max="27" width="14.703125" customWidth="1"/>
-    <col min="28" max="28" width="26.1171875" customWidth="1"/>
+    <col min="24" max="26" width="14.125" customWidth="1"/>
+    <col min="27" max="27" width="14.75" customWidth="1"/>
+    <col min="28" max="28" width="26.125" customWidth="1"/>
     <col min="29" max="29" width="25" customWidth="1"/>
-    <col min="30" max="32" width="16.29296875" customWidth="1"/>
-    <col min="33" max="33" width="12.29296875" customWidth="1"/>
+    <col min="30" max="32" width="16.25" customWidth="1"/>
+    <col min="33" max="33" width="12.25" customWidth="1"/>
     <col min="34" max="34" width="25" customWidth="1"/>
-    <col min="35" max="35" width="12.46875" customWidth="1"/>
-    <col min="36" max="37" width="10.703125" customWidth="1"/>
+    <col min="35" max="35" width="12.5" customWidth="1"/>
+    <col min="36" max="37" width="10.75" customWidth="1"/>
     <col min="38" max="39" width="12" customWidth="1"/>
-    <col min="41" max="41" width="23.703125" customWidth="1"/>
-    <col min="42" max="43" width="25.8203125" customWidth="1"/>
+    <col min="41" max="41" width="23.75" customWidth="1"/>
+    <col min="42" max="43" width="25.875" customWidth="1"/>
     <col min="44" max="44" width="21" customWidth="1"/>
-    <col min="45" max="47" width="25.8203125" customWidth="1"/>
-    <col min="48" max="48" width="16.29296875" customWidth="1"/>
+    <col min="45" max="47" width="25.875" customWidth="1"/>
+    <col min="48" max="48" width="16.25" customWidth="1"/>
     <col min="49" max="49" width="17" customWidth="1"/>
-    <col min="50" max="51" width="16.1171875" customWidth="1"/>
-    <col min="52" max="52" width="9.29296875" customWidth="1"/>
-    <col min="53" max="53" width="12.46875" customWidth="1"/>
-    <col min="55" max="55" width="23.8203125" customWidth="1"/>
-    <col min="56" max="56" width="15.46875" customWidth="1"/>
-    <col min="57" max="57" width="11.234375" customWidth="1"/>
-    <col min="58" max="58" width="12.1171875" customWidth="1"/>
-    <col min="59" max="60" width="12.17578125" bestFit="1" customWidth="1"/>
+    <col min="50" max="51" width="16.125" customWidth="1"/>
+    <col min="52" max="52" width="9.25" customWidth="1"/>
+    <col min="53" max="53" width="12.5" customWidth="1"/>
+    <col min="55" max="55" width="23.875" customWidth="1"/>
+    <col min="56" max="56" width="15.5" customWidth="1"/>
+    <col min="57" max="57" width="11.25" customWidth="1"/>
+    <col min="58" max="58" width="12.125" customWidth="1"/>
+    <col min="59" max="60" width="12.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:61" ht="15.35" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:61" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -863,7 +867,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="2" spans="1:61" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:61" x14ac:dyDescent="0.2">
       <c r="AH2" s="2"/>
       <c r="AI2" s="2"/>
       <c r="AJ2" s="2"/>
@@ -878,13 +882,13 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{71B27B56-1823-4D07-9234-02F082420C5C}">
-  <dimension ref="A1:L1"/>
-  <sheetFormatPr defaultColWidth="8.8203125" defaultRowHeight="14" x14ac:dyDescent="0.45"/>
+  <dimension ref="A1:M1"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="3" max="3" width="10.8203125" customWidth="1"/>
+    <col min="3" max="3" width="10.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -898,27 +902,30 @@
         <v>46</v>
       </c>
       <c r="E1" t="s">
+        <v>71</v>
+      </c>
+      <c r="F1" t="s">
         <v>54</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>47</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>48</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>49</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>50</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>51</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>52</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>24</v>
       </c>
     </row>

--- a/src/src/main/webapp/portal/wo/woExport/APM_WorkOrder_Template.xlsx
+++ b/src/src/main/webapp/portal/wo/woExport/APM_WorkOrder_Template.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26924"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27928"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD361C61-00A6-4BBD-BA79-D9264D1A06B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4838D564-7BBC-426B-AECE-DF16C96EB928}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13992" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="WorkOrder List" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="75">
   <si>
     <t>报修单号</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -303,17 +303,26 @@
   <si>
     <t>备件类别</t>
     <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>工单分类</t>
+  </si>
+  <si>
+    <t>协作者工时填写方式</t>
+  </si>
+  <si>
+    <t>协作者工时详情</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -326,7 +335,7 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="等线"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -334,7 +343,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -644,45 +653,48 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:BI2"/>
-  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:BL2"/>
+  <sheetFormatPr defaultColWidth="8.89453125" defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="4" width="20.5" customWidth="1"/>
-    <col min="5" max="6" width="23.125" customWidth="1"/>
-    <col min="7" max="7" width="16.25" customWidth="1"/>
-    <col min="8" max="17" width="17.5" customWidth="1"/>
-    <col min="18" max="18" width="20.25" customWidth="1"/>
-    <col min="19" max="20" width="16.25" customWidth="1"/>
-    <col min="21" max="21" width="15.875" customWidth="1"/>
-    <col min="22" max="22" width="25.25" customWidth="1"/>
+    <col min="2" max="4" width="20.47265625" customWidth="1"/>
+    <col min="5" max="6" width="23.1015625" customWidth="1"/>
+    <col min="7" max="7" width="16.26171875" customWidth="1"/>
+    <col min="8" max="17" width="17.47265625" customWidth="1"/>
+    <col min="18" max="18" width="20.26171875" customWidth="1"/>
+    <col min="19" max="20" width="16.26171875" customWidth="1"/>
+    <col min="21" max="21" width="15.89453125" customWidth="1"/>
+    <col min="22" max="22" width="25.26171875" customWidth="1"/>
     <col min="23" max="23" width="23" customWidth="1"/>
-    <col min="24" max="26" width="14.125" customWidth="1"/>
-    <col min="27" max="27" width="14.75" customWidth="1"/>
-    <col min="28" max="28" width="26.125" customWidth="1"/>
+    <col min="24" max="26" width="14.1015625" customWidth="1"/>
+    <col min="27" max="27" width="14.734375" customWidth="1"/>
+    <col min="28" max="28" width="26.1015625" customWidth="1"/>
     <col min="29" max="29" width="25" customWidth="1"/>
-    <col min="30" max="32" width="16.25" customWidth="1"/>
-    <col min="33" max="33" width="12.25" customWidth="1"/>
+    <col min="30" max="32" width="16.26171875" customWidth="1"/>
+    <col min="33" max="33" width="12.26171875" customWidth="1"/>
     <col min="34" max="34" width="25" customWidth="1"/>
-    <col min="35" max="35" width="12.5" customWidth="1"/>
-    <col min="36" max="37" width="10.75" customWidth="1"/>
+    <col min="35" max="35" width="12.47265625" customWidth="1"/>
+    <col min="36" max="37" width="10.734375" customWidth="1"/>
     <col min="38" max="39" width="12" customWidth="1"/>
-    <col min="41" max="41" width="23.75" customWidth="1"/>
-    <col min="42" max="43" width="25.875" customWidth="1"/>
+    <col min="41" max="41" width="23.734375" customWidth="1"/>
+    <col min="42" max="43" width="25.89453125" customWidth="1"/>
     <col min="44" max="44" width="21" customWidth="1"/>
-    <col min="45" max="47" width="25.875" customWidth="1"/>
-    <col min="48" max="48" width="16.25" customWidth="1"/>
+    <col min="45" max="47" width="25.89453125" customWidth="1"/>
+    <col min="48" max="48" width="16.26171875" customWidth="1"/>
     <col min="49" max="49" width="17" customWidth="1"/>
-    <col min="50" max="51" width="16.125" customWidth="1"/>
-    <col min="52" max="52" width="9.25" customWidth="1"/>
-    <col min="53" max="53" width="12.5" customWidth="1"/>
-    <col min="55" max="55" width="23.875" customWidth="1"/>
-    <col min="56" max="56" width="15.5" customWidth="1"/>
-    <col min="57" max="57" width="11.25" customWidth="1"/>
-    <col min="58" max="58" width="12.125" customWidth="1"/>
-    <col min="59" max="60" width="12.125" bestFit="1" customWidth="1"/>
+    <col min="50" max="51" width="16.1015625" customWidth="1"/>
+    <col min="52" max="52" width="9.26171875" customWidth="1"/>
+    <col min="53" max="53" width="12.47265625" customWidth="1"/>
+    <col min="55" max="55" width="23.89453125" customWidth="1"/>
+    <col min="56" max="56" width="15.47265625" customWidth="1"/>
+    <col min="57" max="57" width="11.26171875" customWidth="1"/>
+    <col min="58" max="58" width="12.1015625" customWidth="1"/>
+    <col min="59" max="59" width="15.41796875" customWidth="1"/>
+    <col min="60" max="60" width="18" customWidth="1"/>
+    <col min="61" max="61" width="20.05078125" customWidth="1"/>
+    <col min="62" max="62" width="23.47265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:61" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:64" ht="15.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -864,10 +876,19 @@
         <v>69</v>
       </c>
       <c r="BI1" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="BJ1" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="BK1" s="1" t="s">
         <v>70</v>
       </c>
+      <c r="BL1" s="1" t="s">
+        <v>72</v>
+      </c>
     </row>
-    <row r="2" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:64">
       <c r="AH2" s="2"/>
       <c r="AI2" s="2"/>
       <c r="AJ2" s="2"/>
@@ -883,12 +904,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{71B27B56-1823-4D07-9234-02F082420C5C}">
   <dimension ref="A1:M1"/>
-  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.89453125" defaultRowHeight="14.4"/>
   <cols>
-    <col min="3" max="3" width="10.875" customWidth="1"/>
+    <col min="3" max="3" width="10.89453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:13">
       <c r="A1" t="s">
         <v>0</v>
       </c>
